--- a/Rekap Barang September.xlsx
+++ b/Rekap Barang September.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCA6F1B-57E9-43E5-BED1-50C37E4DDC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74A21FB-A1B6-4B84-AB50-1B03AE498268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F7CA82D4-8FEC-46C5-8E3D-E43D8F29F763}"/>
   </bookViews>
@@ -4108,7 +4108,9 @@
       <c r="D58" s="30">
         <v>16</v>
       </c>
-      <c r="E58" s="30"/>
+      <c r="E58" s="30">
+        <v>2</v>
+      </c>
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
@@ -4140,7 +4142,7 @@
       <c r="AH58" s="30"/>
       <c r="AI58" s="5">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AJ58" s="27"/>
       <c r="AK58" s="2"/>
@@ -4264,7 +4266,9 @@
         <v>3</v>
       </c>
       <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
+      <c r="E61" s="30">
+        <v>1</v>
+      </c>
       <c r="F61" s="30"/>
       <c r="G61" s="30"/>
       <c r="H61" s="30"/>
@@ -4296,7 +4300,7 @@
       <c r="AH61" s="30"/>
       <c r="AI61" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ61" s="27"/>
       <c r="AK61" s="2"/>

--- a/Rekap Barang September.xlsx
+++ b/Rekap Barang September.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74A21FB-A1B6-4B84-AB50-1B03AE498268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955CA32D-9B98-40E5-BFC8-DE20F3963606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F7CA82D4-8FEC-46C5-8E3D-E43D8F29F763}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="161">
   <si>
     <t>No</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>Drainer Pump AC</t>
+  </si>
+  <si>
+    <t>Ezviz TY1 Pro 2k</t>
   </si>
 </sst>
 </file>
@@ -681,7 +684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -770,6 +773,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -779,17 +785,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1125,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551225FE-23E4-42F3-B08F-0D37368591A6}">
-  <dimension ref="A1:AO194"/>
+  <dimension ref="A1:AO195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="9" customWidth="1"/>
@@ -1139,50 +1151,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="45"/>
+      <c r="AD1" s="45"/>
+      <c r="AE1" s="45"/>
+      <c r="AF1" s="45"/>
+      <c r="AG1" s="45"/>
+      <c r="AH1" s="45"/>
+      <c r="AI1" s="45"/>
       <c r="AJ1" s="8"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="42"/>
       <c r="AI2" s="12"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
@@ -1292,13 +1304,13 @@
         <v>3</v>
       </c>
       <c r="AJ3" s="16"/>
-      <c r="AK3" s="38" t="s">
+      <c r="AK3" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="41"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -1312,9 +1324,13 @@
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="7">
+        <v>1</v>
+      </c>
       <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="H4" s="7">
+        <v>2</v>
+      </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -1343,7 +1359,7 @@
       <c r="AH4" s="7"/>
       <c r="AI4" s="6">
         <f>C4-D4-E4-F4-G4-H4-I4-J4-K4-L4-M4-N4-O4-P4-Q4-R4-S4-T4-U4-V4-W4-X4-Y4-Z4-AA4-AB4-AC4-AD4-AE4-AF4-AG4-AH4</f>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AJ4" s="16"/>
       <c r="AK4" s="2"/>
@@ -1366,9 +1382,13 @@
         <v>3</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="F5" s="7">
+        <v>1</v>
+      </c>
       <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -1396,8 +1416,8 @@
       <c r="AG5" s="7"/>
       <c r="AH5" s="7"/>
       <c r="AI5" s="6">
-        <f t="shared" ref="AI5:AI27" si="0">C5-D5-E5-F5-G5-H5-I5-J5-K5-L5-M5-N5-O5-P5-Q5-R5-S5-T5-U5-V5-W5-X5-Y5-Z5-AA5-AB5-AC5-AD5-AE5-AF5-AG5-AH5</f>
-        <v>46</v>
+        <f t="shared" ref="AI5:AI28" si="0">C5-D5-E5-F5-G5-H5-I5-J5-K5-L5-M5-N5-O5-P5-Q5-R5-S5-T5-U5-V5-W5-X5-Y5-Z5-AA5-AB5-AC5-AD5-AE5-AF5-AG5-AH5</f>
+        <v>42</v>
       </c>
       <c r="AJ5" s="16"/>
       <c r="AK5" s="2"/>
@@ -2187,14 +2207,12 @@
       <c r="AO20" s="2"/>
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>18</v>
-      </c>
+      <c r="A21" s="6"/>
       <c r="B21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="3">
-        <v>10</v>
+        <v>160</v>
+      </c>
+      <c r="C21" s="38">
+        <v>30</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -2229,10 +2247,12 @@
       <c r="AH21" s="7"/>
       <c r="AI21" s="6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AJ21" s="16"/>
-      <c r="AK21" s="2"/>
+      <c r="AK21" s="46">
+        <v>46151</v>
+      </c>
       <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
@@ -2240,13 +2260,13 @@
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -2281,10 +2301,10 @@
       <c r="AH22" s="7"/>
       <c r="AI22" s="6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AJ22" s="16"/>
-      <c r="AK22" s="2"/>
+      <c r="AK22" s="47"/>
       <c r="AL22" s="2"/>
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
@@ -2292,13 +2312,13 @@
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -2333,10 +2353,12 @@
       <c r="AH23" s="7"/>
       <c r="AI23" s="6">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AJ23" s="16"/>
-      <c r="AK23" s="2"/>
+      <c r="AK23" s="46">
+        <v>46151</v>
+      </c>
       <c r="AL23" s="2"/>
       <c r="AM23" s="2"/>
       <c r="AN23" s="2"/>
@@ -2344,13 +2366,13 @@
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -2385,7 +2407,7 @@
       <c r="AH24" s="7"/>
       <c r="AI24" s="6">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AJ24" s="16"/>
       <c r="AK24" s="2"/>
@@ -2396,13 +2418,13 @@
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -2437,7 +2459,7 @@
       <c r="AH25" s="7"/>
       <c r="AI25" s="6">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" s="16"/>
       <c r="AK25" s="2"/>
@@ -2448,13 +2470,13 @@
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -2489,7 +2511,7 @@
       <c r="AH26" s="7"/>
       <c r="AI26" s="6">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ26" s="16"/>
       <c r="AK26" s="2"/>
@@ -2500,13 +2522,13 @@
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="6">
-        <v>4</v>
+        <v>56</v>
+      </c>
+      <c r="C27" s="3">
+        <v>7</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -2541,7 +2563,7 @@
       <c r="AH27" s="7"/>
       <c r="AI27" s="6">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ27" s="16"/>
       <c r="AK27" s="2"/>
@@ -2551,47 +2573,56 @@
       <c r="AO27" s="2"/>
     </row>
     <row r="28" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="17"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="17"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="17"/>
-      <c r="AF28" s="17"/>
-      <c r="AG28" s="17"/>
-      <c r="AH28" s="17"/>
-      <c r="AI28" s="16"/>
+      <c r="A28" s="6">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="7"/>
+      <c r="AA28" s="7"/>
+      <c r="AB28" s="7"/>
+      <c r="AC28" s="7"/>
+      <c r="AD28" s="7"/>
+      <c r="AE28" s="7"/>
+      <c r="AF28" s="7"/>
+      <c r="AG28" s="7"/>
+      <c r="AH28" s="7"/>
+      <c r="AI28" s="6">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="AJ28" s="16"/>
-      <c r="AK28" s="12"/>
-      <c r="AL28" s="12"/>
-      <c r="AM28" s="12"/>
-      <c r="AN28" s="12"/>
-      <c r="AO28" s="12"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
+      <c r="AM28" s="2"/>
+      <c r="AN28" s="2"/>
+      <c r="AO28" s="2"/>
     </row>
     <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
@@ -2628,7 +2659,13 @@
       <c r="AF29" s="17"/>
       <c r="AG29" s="17"/>
       <c r="AH29" s="17"/>
-      <c r="AI29" s="12"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="16"/>
+      <c r="AK29" s="12"/>
+      <c r="AL29" s="12"/>
+      <c r="AM29" s="12"/>
+      <c r="AN29" s="12"/>
+      <c r="AO29" s="12"/>
     </row>
     <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
@@ -2705,193 +2742,180 @@
       <c r="AI31" s="12"/>
     </row>
     <row r="32" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="17"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="17"/>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="17"/>
+      <c r="AA32" s="17"/>
+      <c r="AB32" s="17"/>
+      <c r="AC32" s="17"/>
+      <c r="AD32" s="17"/>
+      <c r="AE32" s="17"/>
+      <c r="AF32" s="17"/>
+      <c r="AG32" s="17"/>
+      <c r="AH32" s="17"/>
+      <c r="AI32" s="12"/>
+    </row>
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A33" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="43"/>
-    </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="B33" s="42"/>
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B34" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C34" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D34" s="14">
         <v>1</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E34" s="14">
         <v>2</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F34" s="14">
         <v>3</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G34" s="14">
         <v>4</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H34" s="14">
         <v>5</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I34" s="14">
         <v>6</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J34" s="14">
         <v>7</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K34" s="14">
         <v>8</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L34" s="14">
         <v>9</v>
       </c>
-      <c r="M33" s="14">
+      <c r="M34" s="14">
         <v>10</v>
       </c>
-      <c r="N33" s="14">
+      <c r="N34" s="14">
         <v>11</v>
       </c>
-      <c r="O33" s="14">
+      <c r="O34" s="14">
         <v>12</v>
       </c>
-      <c r="P33" s="14">
+      <c r="P34" s="14">
         <v>13</v>
       </c>
-      <c r="Q33" s="14">
+      <c r="Q34" s="14">
         <v>14</v>
       </c>
-      <c r="R33" s="14">
+      <c r="R34" s="14">
         <v>15</v>
       </c>
-      <c r="S33" s="14">
+      <c r="S34" s="14">
         <v>16</v>
       </c>
-      <c r="T33" s="14">
+      <c r="T34" s="14">
         <v>17</v>
       </c>
-      <c r="U33" s="14">
+      <c r="U34" s="14">
         <v>18</v>
       </c>
-      <c r="V33" s="14">
+      <c r="V34" s="14">
         <v>19</v>
       </c>
-      <c r="W33" s="14">
+      <c r="W34" s="14">
         <v>20</v>
       </c>
-      <c r="X33" s="14">
+      <c r="X34" s="14">
         <v>21</v>
       </c>
-      <c r="Y33" s="14">
+      <c r="Y34" s="14">
         <v>22</v>
       </c>
-      <c r="Z33" s="14">
+      <c r="Z34" s="14">
         <v>23</v>
       </c>
-      <c r="AA33" s="14">
+      <c r="AA34" s="14">
         <v>24</v>
       </c>
-      <c r="AB33" s="14">
+      <c r="AB34" s="14">
         <v>25</v>
       </c>
-      <c r="AC33" s="14">
+      <c r="AC34" s="14">
         <v>26</v>
       </c>
-      <c r="AD33" s="14">
+      <c r="AD34" s="14">
         <v>27</v>
       </c>
-      <c r="AE33" s="14">
+      <c r="AE34" s="14">
         <v>28</v>
       </c>
-      <c r="AF33" s="14">
+      <c r="AF34" s="14">
         <v>29</v>
       </c>
-      <c r="AG33" s="14">
+      <c r="AG34" s="14">
         <v>30</v>
       </c>
-      <c r="AH33" s="14">
+      <c r="AH34" s="14">
         <v>31</v>
       </c>
-      <c r="AI33" s="15" t="s">
+      <c r="AI34" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="AJ33" s="16"/>
-      <c r="AK33" s="38" t="s">
+      <c r="AJ34" s="16"/>
+      <c r="AK34" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AL33" s="39"/>
-      <c r="AM33" s="39"/>
-      <c r="AN33" s="39"/>
-      <c r="AO33" s="40"/>
-    </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>1</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="6">
-        <v>4</v>
-      </c>
-      <c r="D34" s="7">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="X34" s="7"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="7"/>
-      <c r="AC34" s="7"/>
-      <c r="AD34" s="7"/>
-      <c r="AE34" s="7"/>
-      <c r="AF34" s="7"/>
-      <c r="AG34" s="7"/>
-      <c r="AH34" s="7"/>
-      <c r="AI34" s="6">
-        <f>C34-D34-E34-F34-G34-H34-I34-J34-K34-L34-M34-N34-O34-P34-Q34-R34-S34-T34-U34-V34-W34-X34-Y34-Z34-AA34-AB34-AC34-AD34-AE34-AF34-AG34-AH34</f>
-        <v>3</v>
-      </c>
-      <c r="AJ34" s="16"/>
-      <c r="AK34" s="2"/>
-      <c r="AL34" s="2"/>
-      <c r="AM34" s="2"/>
-      <c r="AN34" s="2"/>
-      <c r="AO34" s="2"/>
+      <c r="AL34" s="40"/>
+      <c r="AM34" s="40"/>
+      <c r="AN34" s="40"/>
+      <c r="AO34" s="41"/>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35" s="6">
         <v>4</v>
       </c>
-      <c r="D35" s="7"/>
+      <c r="D35" s="7">
+        <v>1</v>
+      </c>
       <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -2921,8 +2945,8 @@
       <c r="AG35" s="7"/>
       <c r="AH35" s="7"/>
       <c r="AI35" s="6">
-        <f t="shared" ref="AI35:AI45" si="1">C35-D35-E35-F35-G35-H35-I35-J35-K35-L35-M35-N35-O35-P35-Q35-R35-S35-T35-U35-V35-W35-X35-Y35-Z35-AA35-AB35-AC35-AD35-AE35-AF35-AG35-AH35</f>
-        <v>4</v>
+        <f>C35-D35-E35-F35-G35-H35-I35-J35-K35-L35-M35-N35-O35-P35-Q35-R35-S35-T35-U35-V35-W35-X35-Y35-Z35-AA35-AB35-AC35-AD35-AE35-AF35-AG35-AH35</f>
+        <v>2</v>
       </c>
       <c r="AJ35" s="16"/>
       <c r="AK35" s="2"/>
@@ -2933,13 +2957,13 @@
     </row>
     <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C36" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -2973,8 +2997,8 @@
       <c r="AG36" s="7"/>
       <c r="AH36" s="7"/>
       <c r="AI36" s="6">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" ref="AI36:AI46" si="1">C36-D36-E36-F36-G36-H36-I36-J36-K36-L36-M36-N36-O36-P36-Q36-R36-S36-T36-U36-V36-W36-X36-Y36-Z36-AA36-AB36-AC36-AD36-AE36-AF36-AG36-AH36</f>
+        <v>4</v>
       </c>
       <c r="AJ36" s="16"/>
       <c r="AK36" s="2"/>
@@ -2985,13 +3009,13 @@
     </row>
     <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="10">
         <v>3</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -3026,7 +3050,7 @@
       <c r="AH37" s="7"/>
       <c r="AI37" s="6">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ37" s="16"/>
       <c r="AK37" s="2"/>
@@ -3037,13 +3061,13 @@
     </row>
     <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="6">
-        <v>4</v>
+        <v>27</v>
+      </c>
+      <c r="C38" s="10">
+        <v>3</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -3078,7 +3102,7 @@
       <c r="AH38" s="7"/>
       <c r="AI38" s="6">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ38" s="16"/>
       <c r="AK38" s="2"/>
@@ -3089,13 +3113,13 @@
     </row>
     <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -3130,7 +3154,7 @@
       <c r="AH39" s="7"/>
       <c r="AI39" s="6">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ39" s="16"/>
       <c r="AK39" s="2"/>
@@ -3141,13 +3165,13 @@
     </row>
     <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C40" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -3182,7 +3206,7 @@
       <c r="AH40" s="7"/>
       <c r="AI40" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ40" s="16"/>
       <c r="AK40" s="2"/>
@@ -3193,13 +3217,13 @@
     </row>
     <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C41" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -3234,7 +3258,7 @@
       <c r="AH41" s="7"/>
       <c r="AI41" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ41" s="16"/>
       <c r="AK41" s="2"/>
@@ -3245,10 +3269,10 @@
     </row>
     <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C42" s="6">
         <v>1</v>
@@ -3297,13 +3321,13 @@
     </row>
     <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C43" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -3338,7 +3362,7 @@
       <c r="AH43" s="7"/>
       <c r="AI43" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ43" s="16"/>
       <c r="AK43" s="2"/>
@@ -3349,10 +3373,10 @@
     </row>
     <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" s="6">
         <v>0</v>
@@ -3401,10 +3425,10 @@
     </row>
     <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C45" s="6">
         <v>0</v>
@@ -3452,46 +3476,56 @@
       <c r="AO45" s="2"/>
     </row>
     <row r="46" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A46" s="16"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-      <c r="K46" s="17"/>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17"/>
-      <c r="O46" s="17"/>
-      <c r="P46" s="17"/>
-      <c r="Q46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
-      <c r="U46" s="17"/>
-      <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="17"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="17"/>
-      <c r="AA46" s="17"/>
-      <c r="AB46" s="17"/>
-      <c r="AC46" s="17"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="17"/>
-      <c r="AF46" s="17"/>
-      <c r="AG46" s="17"/>
-      <c r="AH46" s="17"/>
-      <c r="AI46" s="12"/>
-      <c r="AK46" s="12"/>
-      <c r="AL46" s="12"/>
-      <c r="AM46" s="12"/>
-      <c r="AN46" s="12"/>
-      <c r="AO46" s="12"/>
+      <c r="A46" s="6">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
+      <c r="Y46" s="7"/>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="7"/>
+      <c r="AB46" s="7"/>
+      <c r="AC46" s="7"/>
+      <c r="AD46" s="7"/>
+      <c r="AE46" s="7"/>
+      <c r="AF46" s="7"/>
+      <c r="AG46" s="7"/>
+      <c r="AH46" s="7"/>
+      <c r="AI46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="16"/>
+      <c r="AK46" s="2"/>
+      <c r="AL46" s="2"/>
+      <c r="AM46" s="2"/>
+      <c r="AN46" s="2"/>
+      <c r="AO46" s="2"/>
     </row>
     <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
@@ -3620,44 +3654,41 @@
       <c r="AO49" s="12"/>
     </row>
     <row r="50" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A50" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="41"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19"/>
-      <c r="O50" s="19"/>
-      <c r="P50" s="19"/>
-      <c r="Q50" s="19"/>
-      <c r="R50" s="19"/>
-      <c r="S50" s="19"/>
-      <c r="T50" s="19"/>
-      <c r="U50" s="19"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="19"/>
-      <c r="X50" s="19"/>
-      <c r="Y50" s="19"/>
-      <c r="Z50" s="19"/>
-      <c r="AA50" s="19"/>
-      <c r="AB50" s="19"/>
-      <c r="AC50" s="19"/>
-      <c r="AD50" s="19"/>
-      <c r="AE50" s="19"/>
-      <c r="AF50" s="19"/>
-      <c r="AG50" s="19"/>
-      <c r="AH50" s="19"/>
-      <c r="AI50" s="20"/>
-      <c r="AJ50" s="21"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="17"/>
+      <c r="AA50" s="17"/>
+      <c r="AB50" s="17"/>
+      <c r="AC50" s="17"/>
+      <c r="AD50" s="17"/>
+      <c r="AE50" s="17"/>
+      <c r="AF50" s="17"/>
+      <c r="AG50" s="17"/>
+      <c r="AH50" s="17"/>
+      <c r="AI50" s="12"/>
       <c r="AK50" s="12"/>
       <c r="AL50" s="12"/>
       <c r="AM50" s="12"/>
@@ -3665,187 +3696,182 @@
       <c r="AO50" s="12"/>
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="43"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="19"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19"/>
+      <c r="R51" s="19"/>
+      <c r="S51" s="19"/>
+      <c r="T51" s="19"/>
+      <c r="U51" s="19"/>
+      <c r="V51" s="19"/>
+      <c r="W51" s="19"/>
+      <c r="X51" s="19"/>
+      <c r="Y51" s="19"/>
+      <c r="Z51" s="19"/>
+      <c r="AA51" s="19"/>
+      <c r="AB51" s="19"/>
+      <c r="AC51" s="19"/>
+      <c r="AD51" s="19"/>
+      <c r="AE51" s="19"/>
+      <c r="AF51" s="19"/>
+      <c r="AG51" s="19"/>
+      <c r="AH51" s="19"/>
+      <c r="AI51" s="20"/>
+      <c r="AJ51" s="21"/>
+      <c r="AK51" s="12"/>
+      <c r="AL51" s="12"/>
+      <c r="AM51" s="12"/>
+      <c r="AN51" s="12"/>
+      <c r="AO51" s="12"/>
+    </row>
+    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A52" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B52" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C52" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D52" s="25">
         <v>1</v>
       </c>
-      <c r="E51" s="25">
+      <c r="E52" s="25">
         <v>2</v>
       </c>
-      <c r="F51" s="25">
+      <c r="F52" s="25">
         <v>3</v>
       </c>
-      <c r="G51" s="25">
+      <c r="G52" s="25">
         <v>4</v>
       </c>
-      <c r="H51" s="25">
+      <c r="H52" s="25">
         <v>5</v>
       </c>
-      <c r="I51" s="25">
+      <c r="I52" s="25">
         <v>6</v>
       </c>
-      <c r="J51" s="25">
+      <c r="J52" s="25">
         <v>7</v>
       </c>
-      <c r="K51" s="25">
+      <c r="K52" s="25">
         <v>8</v>
       </c>
-      <c r="L51" s="25">
+      <c r="L52" s="25">
         <v>9</v>
       </c>
-      <c r="M51" s="25">
+      <c r="M52" s="25">
         <v>10</v>
       </c>
-      <c r="N51" s="25">
+      <c r="N52" s="25">
         <v>11</v>
       </c>
-      <c r="O51" s="25">
+      <c r="O52" s="25">
         <v>12</v>
       </c>
-      <c r="P51" s="25">
+      <c r="P52" s="25">
         <v>13</v>
       </c>
-      <c r="Q51" s="25">
+      <c r="Q52" s="25">
         <v>14</v>
       </c>
-      <c r="R51" s="25">
+      <c r="R52" s="25">
         <v>15</v>
       </c>
-      <c r="S51" s="25">
+      <c r="S52" s="25">
         <v>16</v>
       </c>
-      <c r="T51" s="25">
+      <c r="T52" s="25">
         <v>17</v>
       </c>
-      <c r="U51" s="25">
+      <c r="U52" s="25">
         <v>18</v>
       </c>
-      <c r="V51" s="25">
+      <c r="V52" s="25">
         <v>19</v>
       </c>
-      <c r="W51" s="25">
+      <c r="W52" s="25">
         <v>20</v>
       </c>
-      <c r="X51" s="25">
+      <c r="X52" s="25">
         <v>21</v>
       </c>
-      <c r="Y51" s="25">
+      <c r="Y52" s="25">
         <v>22</v>
       </c>
-      <c r="Z51" s="25">
+      <c r="Z52" s="25">
         <v>23</v>
       </c>
-      <c r="AA51" s="25">
+      <c r="AA52" s="25">
         <v>24</v>
       </c>
-      <c r="AB51" s="25">
+      <c r="AB52" s="25">
         <v>25</v>
       </c>
-      <c r="AC51" s="25">
+      <c r="AC52" s="25">
         <v>26</v>
       </c>
-      <c r="AD51" s="25">
+      <c r="AD52" s="25">
         <v>27</v>
       </c>
-      <c r="AE51" s="25">
+      <c r="AE52" s="25">
         <v>28</v>
       </c>
-      <c r="AF51" s="25">
+      <c r="AF52" s="25">
         <v>29</v>
       </c>
-      <c r="AG51" s="25">
+      <c r="AG52" s="25">
         <v>30</v>
       </c>
-      <c r="AH51" s="25">
+      <c r="AH52" s="25">
         <v>31</v>
       </c>
-      <c r="AI51" s="26" t="s">
+      <c r="AI52" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="AJ51" s="27"/>
-      <c r="AK51" s="38" t="s">
+      <c r="AJ52" s="27"/>
+      <c r="AK52" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AL51" s="39"/>
-      <c r="AM51" s="39"/>
-      <c r="AN51" s="39"/>
-      <c r="AO51" s="40"/>
-    </row>
-    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A52" s="28">
-        <v>1</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C52" s="29">
-        <v>7</v>
-      </c>
-      <c r="D52" s="30">
-        <v>1</v>
-      </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
-      <c r="AA52" s="30"/>
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
-      <c r="AE52" s="30"/>
-      <c r="AF52" s="30"/>
-      <c r="AG52" s="30"/>
-      <c r="AH52" s="30"/>
-      <c r="AI52" s="5">
-        <f>C52-D52-E52-F52-G52-H52-I52-J52-K52-L52-M52-N52-O52-P52-Q52-R52-S52-T52-U52-V52-W52-X52-Y52-Z52-AA52-AB52-AC52-AD52-AE52-AF52-AG52-AH52</f>
-        <v>6</v>
-      </c>
-      <c r="AJ52" s="27"/>
-      <c r="AK52" s="2"/>
-      <c r="AL52" s="2"/>
-      <c r="AM52" s="2"/>
-      <c r="AN52" s="2"/>
-      <c r="AO52" s="2"/>
+      <c r="AL52" s="40"/>
+      <c r="AM52" s="40"/>
+      <c r="AN52" s="40"/>
+      <c r="AO52" s="41"/>
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" s="28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C53" s="29">
-        <v>11</v>
-      </c>
-      <c r="D53" s="30"/>
+        <v>7</v>
+      </c>
+      <c r="D53" s="30">
+        <v>1</v>
+      </c>
       <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
+      <c r="F53" s="30">
+        <v>1</v>
+      </c>
       <c r="G53" s="30"/>
       <c r="H53" s="30"/>
       <c r="I53" s="30"/>
@@ -3875,8 +3901,8 @@
       <c r="AG53" s="30"/>
       <c r="AH53" s="30"/>
       <c r="AI53" s="5">
-        <f t="shared" ref="AI53:AI83" si="2">C53-D53-E53-F53-G53-H53-I53-J53-K53-L53-M53-N53-O53-P53-Q53-R53-S53-T53-U53-V53-W53-X53-Y53-Z53-AA53-AB53-AC53-AD53-AE53-AF53-AG53-AH53</f>
-        <v>11</v>
+        <f>C53-D53-E53-F53-G53-H53-I53-J53-K53-L53-M53-N53-O53-P53-Q53-R53-S53-T53-U53-V53-W53-X53-Y53-Z53-AA53-AB53-AC53-AD53-AE53-AF53-AG53-AH53</f>
+        <v>5</v>
       </c>
       <c r="AJ53" s="27"/>
       <c r="AK53" s="2"/>
@@ -3887,13 +3913,13 @@
     </row>
     <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" s="28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="29">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D54" s="30"/>
       <c r="E54" s="30"/>
@@ -3927,8 +3953,8 @@
       <c r="AG54" s="30"/>
       <c r="AH54" s="30"/>
       <c r="AI54" s="5">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" ref="AI54:AI84" si="2">C54-D54-E54-F54-G54-H54-I54-J54-K54-L54-M54-N54-O54-P54-Q54-R54-S54-T54-U54-V54-W54-X54-Y54-Z54-AA54-AB54-AC54-AD54-AE54-AF54-AG54-AH54</f>
+        <v>11</v>
       </c>
       <c r="AJ54" s="27"/>
       <c r="AK54" s="2"/>
@@ -3939,13 +3965,13 @@
     </row>
     <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" s="28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C55" s="29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D55" s="30"/>
       <c r="E55" s="30"/>
@@ -3980,7 +4006,7 @@
       <c r="AH55" s="30"/>
       <c r="AI55" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AJ55" s="27"/>
       <c r="AK55" s="2"/>
@@ -3991,13 +4017,13 @@
     </row>
     <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" s="28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56" s="29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56" s="30"/>
       <c r="E56" s="30"/>
@@ -4032,7 +4058,7 @@
       <c r="AH56" s="30"/>
       <c r="AI56" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ56" s="27"/>
       <c r="AK56" s="2"/>
@@ -4043,17 +4069,15 @@
     </row>
     <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" s="28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57" s="29">
-        <v>13</v>
-      </c>
-      <c r="D57" s="30">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D57" s="30"/>
       <c r="E57" s="30"/>
       <c r="F57" s="30"/>
       <c r="G57" s="30"/>
@@ -4085,8 +4109,8 @@
       <c r="AG57" s="30"/>
       <c r="AH57" s="30"/>
       <c r="AI57" s="5">
-        <f>C57-D57-E57-F57-G57-H57-I57-J57-K57-L57-M57-N57-O57-P57-Q57-R57-S57-T57-U57-V57-W57-X57-Y57-Z57-AA57-AB57-AC57-AD57-AE57-AF57-AG57-AH57</f>
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
       <c r="AJ57" s="27"/>
       <c r="AK57" s="2"/>
@@ -4097,20 +4121,18 @@
     </row>
     <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" s="28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="C58" s="29">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D58" s="30">
-        <v>16</v>
-      </c>
-      <c r="E58" s="30">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E58" s="30"/>
       <c r="F58" s="30"/>
       <c r="G58" s="30"/>
       <c r="H58" s="30"/>
@@ -4141,8 +4163,8 @@
       <c r="AG58" s="30"/>
       <c r="AH58" s="30"/>
       <c r="AI58" s="5">
-        <f t="shared" si="2"/>
-        <v>50</v>
+        <f>C58-D58-E58-F58-G58-H58-I58-J58-K58-L58-M58-N58-O58-P58-Q58-R58-S58-T58-U58-V58-W58-X58-Y58-Z58-AA58-AB58-AC58-AD58-AE58-AF58-AG58-AH58</f>
+        <v>10</v>
       </c>
       <c r="AJ58" s="27"/>
       <c r="AK58" s="2"/>
@@ -4153,19 +4175,27 @@
     </row>
     <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" s="28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C59" s="29">
-        <v>26</v>
-      </c>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="D59" s="30">
+        <v>3</v>
+      </c>
+      <c r="E59" s="30">
+        <v>2</v>
+      </c>
+      <c r="F59" s="30">
+        <v>2</v>
+      </c>
       <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
+      <c r="H59" s="30">
+        <v>9</v>
+      </c>
       <c r="I59" s="30"/>
       <c r="J59" s="30"/>
       <c r="K59" s="30"/>
@@ -4194,7 +4224,7 @@
       <c r="AH59" s="30"/>
       <c r="AI59" s="5">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="AJ59" s="27"/>
       <c r="AK59" s="2"/>
@@ -4205,13 +4235,13 @@
     </row>
     <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" s="28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C60" s="29">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D60" s="30"/>
       <c r="E60" s="30"/>
@@ -4246,7 +4276,7 @@
       <c r="AH60" s="30"/>
       <c r="AI60" s="5">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AJ60" s="27"/>
       <c r="AK60" s="2"/>
@@ -4257,18 +4287,16 @@
     </row>
     <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" s="28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C61" s="29">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D61" s="30"/>
-      <c r="E61" s="30">
-        <v>1</v>
-      </c>
+      <c r="E61" s="30"/>
       <c r="F61" s="30"/>
       <c r="G61" s="30"/>
       <c r="H61" s="30"/>
@@ -4300,7 +4328,7 @@
       <c r="AH61" s="30"/>
       <c r="AI61" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AJ61" s="27"/>
       <c r="AK61" s="2"/>
@@ -4311,16 +4339,18 @@
     </row>
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" s="28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C62" s="29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
+      <c r="E62" s="30">
+        <v>1</v>
+      </c>
       <c r="F62" s="30"/>
       <c r="G62" s="30"/>
       <c r="H62" s="30"/>
@@ -4352,7 +4382,7 @@
       <c r="AH62" s="30"/>
       <c r="AI62" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AJ62" s="27"/>
       <c r="AK62" s="2"/>
@@ -4363,13 +4393,13 @@
     </row>
     <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" s="28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" s="29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" s="30"/>
       <c r="E63" s="30"/>
@@ -4404,7 +4434,7 @@
       <c r="AH63" s="30"/>
       <c r="AI63" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AJ63" s="27"/>
       <c r="AK63" s="2"/>
@@ -4415,13 +4445,13 @@
     </row>
     <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" s="28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C64" s="29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" s="30"/>
       <c r="E64" s="30"/>
@@ -4456,7 +4486,7 @@
       <c r="AH64" s="30"/>
       <c r="AI64" s="5">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ64" s="27"/>
       <c r="AK64" s="2"/>
@@ -4467,13 +4497,13 @@
     </row>
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" s="28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C65" s="29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D65" s="30"/>
       <c r="E65" s="30"/>
@@ -4508,7 +4538,7 @@
       <c r="AH65" s="30"/>
       <c r="AI65" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ65" s="27"/>
       <c r="AK65" s="2"/>
@@ -4519,13 +4549,13 @@
     </row>
     <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" s="28">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66" s="29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D66" s="30"/>
       <c r="E66" s="30"/>
@@ -4560,7 +4590,7 @@
       <c r="AH66" s="30"/>
       <c r="AI66" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ66" s="27"/>
       <c r="AK66" s="2"/>
@@ -4571,19 +4601,21 @@
     </row>
     <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" s="28">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C67" s="29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D67" s="30"/>
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
       <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
+      <c r="H67" s="30">
+        <v>1</v>
+      </c>
       <c r="I67" s="30"/>
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
@@ -4612,7 +4644,7 @@
       <c r="AH67" s="30"/>
       <c r="AI67" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AJ67" s="27"/>
       <c r="AK67" s="2"/>
@@ -4623,13 +4655,13 @@
     </row>
     <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" s="28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C68" s="29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D68" s="30"/>
       <c r="E68" s="30"/>
@@ -4664,7 +4696,7 @@
       <c r="AH68" s="30"/>
       <c r="AI68" s="5">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AJ68" s="27"/>
       <c r="AK68" s="2"/>
@@ -4675,13 +4707,13 @@
     </row>
     <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" s="28">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C69" s="29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D69" s="30"/>
       <c r="E69" s="30"/>
@@ -4716,7 +4748,7 @@
       <c r="AH69" s="30"/>
       <c r="AI69" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ69" s="27"/>
       <c r="AK69" s="2"/>
@@ -4727,13 +4759,13 @@
     </row>
     <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" s="28">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C70" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" s="30"/>
       <c r="E70" s="30"/>
@@ -4768,7 +4800,7 @@
       <c r="AH70" s="30"/>
       <c r="AI70" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ70" s="27"/>
       <c r="AK70" s="2"/>
@@ -4779,50 +4811,48 @@
     </row>
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" s="28">
-        <v>20</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C71" s="5">
-        <v>11</v>
-      </c>
-      <c r="D71" s="31">
-        <v>1</v>
-      </c>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="31"/>
-      <c r="M71" s="31"/>
-      <c r="N71" s="31"/>
-      <c r="O71" s="31"/>
-      <c r="P71" s="31"/>
-      <c r="Q71" s="31"/>
-      <c r="R71" s="31"/>
-      <c r="S71" s="31"/>
-      <c r="T71" s="31"/>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
-      <c r="W71" s="31"/>
-      <c r="X71" s="31"/>
-      <c r="Y71" s="31"/>
-      <c r="Z71" s="31"/>
-      <c r="AA71" s="31"/>
-      <c r="AB71" s="31"/>
-      <c r="AC71" s="31"/>
-      <c r="AD71" s="31"/>
-      <c r="AE71" s="31"/>
-      <c r="AF71" s="31"/>
-      <c r="AG71" s="31"/>
-      <c r="AH71" s="31"/>
+        <v>19</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C71" s="29">
+        <v>2</v>
+      </c>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="30"/>
+      <c r="N71" s="30"/>
+      <c r="O71" s="30"/>
+      <c r="P71" s="30"/>
+      <c r="Q71" s="30"/>
+      <c r="R71" s="30"/>
+      <c r="S71" s="30"/>
+      <c r="T71" s="30"/>
+      <c r="U71" s="30"/>
+      <c r="V71" s="30"/>
+      <c r="W71" s="30"/>
+      <c r="X71" s="30"/>
+      <c r="Y71" s="30"/>
+      <c r="Z71" s="30"/>
+      <c r="AA71" s="30"/>
+      <c r="AB71" s="30"/>
+      <c r="AC71" s="30"/>
+      <c r="AD71" s="30"/>
+      <c r="AE71" s="30"/>
+      <c r="AF71" s="30"/>
+      <c r="AG71" s="30"/>
+      <c r="AH71" s="30"/>
       <c r="AI71" s="5">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AJ71" s="27"/>
       <c r="AK71" s="2"/>
@@ -4833,17 +4863,21 @@
     </row>
     <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" s="28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C72" s="5">
-        <v>9</v>
-      </c>
-      <c r="D72" s="31"/>
+        <v>11</v>
+      </c>
+      <c r="D72" s="31">
+        <v>1</v>
+      </c>
       <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
+      <c r="F72" s="31">
+        <v>1</v>
+      </c>
       <c r="G72" s="31"/>
       <c r="H72" s="31"/>
       <c r="I72" s="31"/>
@@ -4885,17 +4919,19 @@
     </row>
     <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" s="28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D73" s="31"/>
       <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
+      <c r="F73" s="31">
+        <v>1</v>
+      </c>
       <c r="G73" s="31"/>
       <c r="H73" s="31"/>
       <c r="I73" s="31"/>
@@ -4926,7 +4962,7 @@
       <c r="AH73" s="31"/>
       <c r="AI73" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AJ73" s="27"/>
       <c r="AK73" s="2"/>
@@ -4937,13 +4973,13 @@
     </row>
     <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" s="28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C74" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D74" s="31"/>
       <c r="E74" s="31"/>
@@ -4978,7 +5014,7 @@
       <c r="AH74" s="31"/>
       <c r="AI74" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ74" s="27"/>
       <c r="AK74" s="2"/>
@@ -4989,13 +5025,13 @@
     </row>
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" s="28">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C75" s="5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D75" s="31"/>
       <c r="E75" s="31"/>
@@ -5030,7 +5066,7 @@
       <c r="AH75" s="31"/>
       <c r="AI75" s="5">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ75" s="27"/>
       <c r="AK75" s="2"/>
@@ -5041,13 +5077,13 @@
     </row>
     <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" s="28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C76" s="5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D76" s="31"/>
       <c r="E76" s="31"/>
@@ -5082,7 +5118,7 @@
       <c r="AH76" s="31"/>
       <c r="AI76" s="5">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AJ76" s="27"/>
       <c r="AK76" s="2"/>
@@ -5093,13 +5129,13 @@
     </row>
     <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" s="28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C77" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D77" s="31"/>
       <c r="E77" s="31"/>
@@ -5134,7 +5170,7 @@
       <c r="AH77" s="31"/>
       <c r="AI77" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ77" s="27"/>
       <c r="AK77" s="2"/>
@@ -5145,13 +5181,13 @@
     </row>
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" s="28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C78" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78" s="31"/>
       <c r="E78" s="31"/>
@@ -5186,7 +5222,7 @@
       <c r="AH78" s="31"/>
       <c r="AI78" s="5">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ78" s="27"/>
       <c r="AK78" s="2"/>
@@ -5197,13 +5233,13 @@
     </row>
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" s="28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" s="31"/>
       <c r="E79" s="31"/>
@@ -5238,7 +5274,7 @@
       <c r="AH79" s="31"/>
       <c r="AI79" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ79" s="27"/>
       <c r="AK79" s="2"/>
@@ -5249,49 +5285,50 @@
     </row>
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" s="28">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C80" s="6">
+        <v>153</v>
+      </c>
+      <c r="C80" s="5">
         <v>1</v>
       </c>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="7"/>
-      <c r="S80" s="7"/>
-      <c r="T80" s="7"/>
-      <c r="U80" s="7"/>
-      <c r="V80" s="7"/>
-      <c r="W80" s="7"/>
-      <c r="X80" s="7"/>
-      <c r="Y80" s="7"/>
-      <c r="Z80" s="7"/>
-      <c r="AA80" s="7"/>
-      <c r="AB80" s="7"/>
-      <c r="AC80" s="7"/>
-      <c r="AD80" s="7"/>
-      <c r="AE80" s="7"/>
-      <c r="AF80" s="7"/>
-      <c r="AG80" s="7"/>
-      <c r="AH80" s="7"/>
-      <c r="AI80" s="32">
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+      <c r="J80" s="31"/>
+      <c r="K80" s="31"/>
+      <c r="L80" s="31"/>
+      <c r="M80" s="31"/>
+      <c r="N80" s="31"/>
+      <c r="O80" s="31"/>
+      <c r="P80" s="31"/>
+      <c r="Q80" s="31"/>
+      <c r="R80" s="31"/>
+      <c r="S80" s="31"/>
+      <c r="T80" s="31"/>
+      <c r="U80" s="31"/>
+      <c r="V80" s="31"/>
+      <c r="W80" s="31"/>
+      <c r="X80" s="31"/>
+      <c r="Y80" s="31"/>
+      <c r="Z80" s="31"/>
+      <c r="AA80" s="31"/>
+      <c r="AB80" s="31"/>
+      <c r="AC80" s="31"/>
+      <c r="AD80" s="31"/>
+      <c r="AE80" s="31"/>
+      <c r="AF80" s="31"/>
+      <c r="AG80" s="31"/>
+      <c r="AH80" s="31"/>
+      <c r="AI80" s="5">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
+      <c r="AJ80" s="27"/>
       <c r="AK80" s="2"/>
       <c r="AL80" s="2"/>
       <c r="AM80" s="2"/>
@@ -5300,13 +5337,13 @@
     </row>
     <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" s="28">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C81" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -5341,7 +5378,7 @@
       <c r="AH81" s="7"/>
       <c r="AI81" s="32">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK81" s="2"/>
       <c r="AL81" s="2"/>
@@ -5351,13 +5388,13 @@
     </row>
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" s="28">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C82" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
@@ -5392,7 +5429,7 @@
       <c r="AH82" s="7"/>
       <c r="AI82" s="32">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK82" s="2"/>
       <c r="AL82" s="2"/>
@@ -5402,13 +5439,13 @@
     </row>
     <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" s="28">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C83" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
@@ -5443,7 +5480,7 @@
       <c r="AH83" s="7"/>
       <c r="AI83" s="32">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AK83" s="2"/>
       <c r="AL83" s="2"/>
@@ -5451,254 +5488,254 @@
       <c r="AN83" s="2"/>
       <c r="AO83" s="2"/>
     </row>
-    <row r="86" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A86" s="41" t="s">
+    <row r="84" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A84" s="28">
+        <v>32</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C84" s="6">
+        <v>5</v>
+      </c>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="7"/>
+      <c r="L84" s="7"/>
+      <c r="M84" s="7"/>
+      <c r="N84" s="7"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="7"/>
+      <c r="Q84" s="7"/>
+      <c r="R84" s="7"/>
+      <c r="S84" s="7"/>
+      <c r="T84" s="7"/>
+      <c r="U84" s="7"/>
+      <c r="V84" s="7"/>
+      <c r="W84" s="7"/>
+      <c r="X84" s="7"/>
+      <c r="Y84" s="7"/>
+      <c r="Z84" s="7"/>
+      <c r="AA84" s="7"/>
+      <c r="AB84" s="7"/>
+      <c r="AC84" s="7"/>
+      <c r="AD84" s="7"/>
+      <c r="AE84" s="7"/>
+      <c r="AF84" s="7"/>
+      <c r="AG84" s="7"/>
+      <c r="AH84" s="7"/>
+      <c r="AI84" s="32">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AK84" s="2"/>
+      <c r="AL84" s="2"/>
+      <c r="AM84" s="2"/>
+      <c r="AN84" s="2"/>
+      <c r="AO84" s="2"/>
+    </row>
+    <row r="87" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A87" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B86" s="41"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
-      <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19"/>
-      <c r="O86" s="19"/>
-      <c r="P86" s="19"/>
-      <c r="Q86" s="19"/>
-      <c r="R86" s="19"/>
-      <c r="S86" s="19"/>
-      <c r="T86" s="19"/>
-      <c r="U86" s="19"/>
-      <c r="V86" s="19"/>
-      <c r="W86" s="19"/>
-      <c r="X86" s="19"/>
-      <c r="Y86" s="19"/>
-      <c r="Z86" s="19"/>
-      <c r="AA86" s="19"/>
-      <c r="AB86" s="19"/>
-      <c r="AC86" s="19"/>
-      <c r="AD86" s="19"/>
-      <c r="AE86" s="19"/>
-      <c r="AF86" s="19"/>
-      <c r="AG86" s="19"/>
-      <c r="AH86" s="19"/>
-      <c r="AI86" s="20"/>
-    </row>
-    <row r="87" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A87" s="22" t="s">
+      <c r="B87" s="43"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="19"/>
+      <c r="E87" s="19"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="19"/>
+      <c r="H87" s="19"/>
+      <c r="I87" s="19"/>
+      <c r="J87" s="19"/>
+      <c r="K87" s="19"/>
+      <c r="L87" s="19"/>
+      <c r="M87" s="19"/>
+      <c r="N87" s="19"/>
+      <c r="O87" s="19"/>
+      <c r="P87" s="19"/>
+      <c r="Q87" s="19"/>
+      <c r="R87" s="19"/>
+      <c r="S87" s="19"/>
+      <c r="T87" s="19"/>
+      <c r="U87" s="19"/>
+      <c r="V87" s="19"/>
+      <c r="W87" s="19"/>
+      <c r="X87" s="19"/>
+      <c r="Y87" s="19"/>
+      <c r="Z87" s="19"/>
+      <c r="AA87" s="19"/>
+      <c r="AB87" s="19"/>
+      <c r="AC87" s="19"/>
+      <c r="AD87" s="19"/>
+      <c r="AE87" s="19"/>
+      <c r="AF87" s="19"/>
+      <c r="AG87" s="19"/>
+      <c r="AH87" s="19"/>
+      <c r="AI87" s="20"/>
+    </row>
+    <row r="88" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A88" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B87" s="23" t="s">
+      <c r="B88" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C87" s="33" t="s">
+      <c r="C88" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="25">
+      <c r="D88" s="25">
         <v>1</v>
       </c>
-      <c r="E87" s="25">
+      <c r="E88" s="25">
         <v>2</v>
       </c>
-      <c r="F87" s="25">
+      <c r="F88" s="25">
         <v>3</v>
       </c>
-      <c r="G87" s="25">
+      <c r="G88" s="25">
         <v>4</v>
       </c>
-      <c r="H87" s="25">
+      <c r="H88" s="25">
         <v>5</v>
       </c>
-      <c r="I87" s="25">
+      <c r="I88" s="25">
         <v>6</v>
       </c>
-      <c r="J87" s="25">
+      <c r="J88" s="25">
         <v>7</v>
       </c>
-      <c r="K87" s="25">
+      <c r="K88" s="25">
         <v>8</v>
       </c>
-      <c r="L87" s="25">
+      <c r="L88" s="25">
         <v>9</v>
       </c>
-      <c r="M87" s="25">
+      <c r="M88" s="25">
         <v>10</v>
       </c>
-      <c r="N87" s="25">
+      <c r="N88" s="25">
         <v>11</v>
       </c>
-      <c r="O87" s="25">
+      <c r="O88" s="25">
         <v>12</v>
       </c>
-      <c r="P87" s="25">
+      <c r="P88" s="25">
         <v>13</v>
       </c>
-      <c r="Q87" s="25">
+      <c r="Q88" s="25">
         <v>14</v>
       </c>
-      <c r="R87" s="25">
+      <c r="R88" s="25">
         <v>15</v>
       </c>
-      <c r="S87" s="25">
+      <c r="S88" s="25">
         <v>16</v>
       </c>
-      <c r="T87" s="25">
+      <c r="T88" s="25">
         <v>17</v>
       </c>
-      <c r="U87" s="25">
+      <c r="U88" s="25">
         <v>18</v>
       </c>
-      <c r="V87" s="25">
+      <c r="V88" s="25">
         <v>19</v>
       </c>
-      <c r="W87" s="25">
+      <c r="W88" s="25">
         <v>20</v>
       </c>
-      <c r="X87" s="25">
+      <c r="X88" s="25">
         <v>21</v>
       </c>
-      <c r="Y87" s="25">
+      <c r="Y88" s="25">
         <v>22</v>
       </c>
-      <c r="Z87" s="25">
+      <c r="Z88" s="25">
         <v>23</v>
       </c>
-      <c r="AA87" s="25">
+      <c r="AA88" s="25">
         <v>24</v>
       </c>
-      <c r="AB87" s="25">
+      <c r="AB88" s="25">
         <v>25</v>
       </c>
-      <c r="AC87" s="25">
+      <c r="AC88" s="25">
         <v>26</v>
       </c>
-      <c r="AD87" s="25">
+      <c r="AD88" s="25">
         <v>27</v>
       </c>
-      <c r="AE87" s="25">
+      <c r="AE88" s="25">
         <v>28</v>
       </c>
-      <c r="AF87" s="25">
+      <c r="AF88" s="25">
         <v>29</v>
       </c>
-      <c r="AG87" s="25">
+      <c r="AG88" s="25">
         <v>30</v>
       </c>
-      <c r="AH87" s="25">
+      <c r="AH88" s="25">
         <v>31</v>
       </c>
-      <c r="AI87" s="24" t="s">
+      <c r="AI88" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="AK87" s="38" t="s">
+      <c r="AK88" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AL87" s="39"/>
-      <c r="AM87" s="39"/>
-      <c r="AN87" s="39"/>
-      <c r="AO87" s="40"/>
-    </row>
-    <row r="88" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
-        <v>1</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C88" s="5">
-        <v>3</v>
-      </c>
-      <c r="D88" s="31"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="31"/>
-      <c r="H88" s="31"/>
-      <c r="I88" s="31"/>
-      <c r="J88" s="31"/>
-      <c r="K88" s="31"/>
-      <c r="L88" s="31"/>
-      <c r="M88" s="31"/>
-      <c r="N88" s="31"/>
-      <c r="O88" s="31"/>
-      <c r="P88" s="31"/>
-      <c r="Q88" s="31"/>
-      <c r="R88" s="31"/>
-      <c r="S88" s="31"/>
-      <c r="T88" s="31"/>
-      <c r="U88" s="31"/>
-      <c r="V88" s="31"/>
-      <c r="W88" s="31"/>
-      <c r="X88" s="31"/>
-      <c r="Y88" s="31"/>
-      <c r="Z88" s="31"/>
-      <c r="AA88" s="31"/>
-      <c r="AB88" s="31"/>
-      <c r="AC88" s="31"/>
-      <c r="AD88" s="31"/>
-      <c r="AE88" s="31"/>
-      <c r="AF88" s="31"/>
-      <c r="AG88" s="31"/>
-      <c r="AH88" s="31"/>
-      <c r="AI88" s="5">
-        <f>C88-E88-F88-G88-H88-I88-J88-K88-M88-N88-O88-P88-Q88-R88-S88-T88-U88-V88-W88-X88-Y88-Z88-AA88-AB88-AC88-AD88-AE88-AF88-AG88-AH88</f>
-        <v>3</v>
-      </c>
-      <c r="AK88" s="2"/>
-      <c r="AL88" s="2"/>
-      <c r="AM88" s="2"/>
-      <c r="AN88" s="2"/>
-      <c r="AO88" s="2"/>
+      <c r="AL88" s="40"/>
+      <c r="AM88" s="40"/>
+      <c r="AN88" s="40"/>
+      <c r="AO88" s="41"/>
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
-        <v>2</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="C89" s="5">
-        <v>1</v>
-      </c>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="7"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="7"/>
-      <c r="T89" s="7"/>
-      <c r="U89" s="7"/>
-      <c r="V89" s="7"/>
-      <c r="W89" s="7"/>
-      <c r="X89" s="7"/>
-      <c r="Y89" s="7"/>
-      <c r="Z89" s="7"/>
-      <c r="AA89" s="7"/>
-      <c r="AB89" s="7"/>
-      <c r="AC89" s="7"/>
-      <c r="AD89" s="7"/>
-      <c r="AE89" s="7"/>
-      <c r="AF89" s="7"/>
-      <c r="AG89" s="7"/>
-      <c r="AH89" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="D89" s="31"/>
+      <c r="E89" s="31"/>
+      <c r="F89" s="31"/>
+      <c r="G89" s="31"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="31"/>
+      <c r="J89" s="31"/>
+      <c r="K89" s="31"/>
+      <c r="L89" s="31"/>
+      <c r="M89" s="31"/>
+      <c r="N89" s="31"/>
+      <c r="O89" s="31"/>
+      <c r="P89" s="31"/>
+      <c r="Q89" s="31"/>
+      <c r="R89" s="31"/>
+      <c r="S89" s="31"/>
+      <c r="T89" s="31"/>
+      <c r="U89" s="31"/>
+      <c r="V89" s="31"/>
+      <c r="W89" s="31"/>
+      <c r="X89" s="31"/>
+      <c r="Y89" s="31"/>
+      <c r="Z89" s="31"/>
+      <c r="AA89" s="31"/>
+      <c r="AB89" s="31"/>
+      <c r="AC89" s="31"/>
+      <c r="AD89" s="31"/>
+      <c r="AE89" s="31"/>
+      <c r="AF89" s="31"/>
+      <c r="AG89" s="31"/>
+      <c r="AH89" s="31"/>
       <c r="AI89" s="5">
-        <f t="shared" ref="AI89:AI120" si="3">C89-E89-F89-G89-H89-I89-J89-K89-M89-N89-O89-P89-Q89-R89-S89-T89-U89-V89-W89-X89-Y89-Z89-AA89-AB89-AC89-AD89-AE89-AF89-AG89-AH89</f>
-        <v>1</v>
+        <f>C89-E89-F89-G89-H89-I89-J89-K89-M89-N89-O89-P89-Q89-R89-S89-T89-U89-V89-W89-X89-Y89-Z89-AA89-AB89-AC89-AD89-AE89-AF89-AG89-AH89</f>
+        <v>3</v>
       </c>
       <c r="AK89" s="2"/>
       <c r="AL89" s="2"/>
@@ -5708,13 +5745,13 @@
     </row>
     <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C90" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -5748,8 +5785,8 @@
       <c r="AG90" s="7"/>
       <c r="AH90" s="7"/>
       <c r="AI90" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" ref="AI90:AI121" si="3">C90-E90-F90-G90-H90-I90-J90-K90-M90-N90-O90-P90-Q90-R90-S90-T90-U90-V90-W90-X90-Y90-Z90-AA90-AB90-AC90-AD90-AE90-AF90-AG90-AH90</f>
+        <v>1</v>
       </c>
       <c r="AK90" s="2"/>
       <c r="AL90" s="2"/>
@@ -5759,13 +5796,13 @@
     </row>
     <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C91" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -5800,7 +5837,7 @@
       <c r="AH91" s="7"/>
       <c r="AI91" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK91" s="2"/>
       <c r="AL91" s="2"/>
@@ -5810,10 +5847,10 @@
     </row>
     <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C92" s="5">
         <v>1</v>
@@ -5861,10 +5898,10 @@
     </row>
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C93" s="5">
         <v>1</v>
@@ -5912,13 +5949,13 @@
     </row>
     <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C94" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
@@ -5953,7 +5990,7 @@
       <c r="AH94" s="7"/>
       <c r="AI94" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK94" s="2"/>
       <c r="AL94" s="2"/>
@@ -5963,13 +6000,13 @@
     </row>
     <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C95" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -6004,7 +6041,7 @@
       <c r="AH95" s="7"/>
       <c r="AI95" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK95" s="2"/>
       <c r="AL95" s="2"/>
@@ -6014,12 +6051,12 @@
     </row>
     <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C96" s="6">
+        <v>67</v>
+      </c>
+      <c r="C96" s="5">
         <v>1</v>
       </c>
       <c r="D96" s="7"/>
@@ -6065,10 +6102,10 @@
     </row>
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C97" s="6">
         <v>1</v>
@@ -6116,10 +6153,10 @@
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -6167,13 +6204,13 @@
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C99" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -6208,7 +6245,7 @@
       <c r="AH99" s="7"/>
       <c r="AI99" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK99" s="2"/>
       <c r="AL99" s="2"/>
@@ -6218,13 +6255,13 @@
     </row>
     <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C100" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -6259,7 +6296,7 @@
       <c r="AH100" s="7"/>
       <c r="AI100" s="5">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK100" s="2"/>
       <c r="AL100" s="2"/>
@@ -6269,13 +6306,13 @@
     </row>
     <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C101" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
@@ -6310,7 +6347,7 @@
       <c r="AH101" s="7"/>
       <c r="AI101" s="5">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AK101" s="2"/>
       <c r="AL101" s="2"/>
@@ -6320,13 +6357,13 @@
     </row>
     <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C102" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
@@ -6361,7 +6398,7 @@
       <c r="AH102" s="7"/>
       <c r="AI102" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AK102" s="2"/>
       <c r="AL102" s="2"/>
@@ -6371,13 +6408,13 @@
     </row>
     <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C103" s="6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
@@ -6412,7 +6449,7 @@
       <c r="AH103" s="7"/>
       <c r="AI103" s="5">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AK103" s="2"/>
       <c r="AL103" s="2"/>
@@ -6422,13 +6459,13 @@
     </row>
     <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C104" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
@@ -6463,7 +6500,7 @@
       <c r="AH104" s="7"/>
       <c r="AI104" s="5">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AK104" s="2"/>
       <c r="AL104" s="2"/>
@@ -6473,13 +6510,13 @@
     </row>
     <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C105" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
@@ -6514,7 +6551,7 @@
       <c r="AH105" s="7"/>
       <c r="AI105" s="5">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AK105" s="2"/>
       <c r="AL105" s="2"/>
@@ -6524,13 +6561,13 @@
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C106" s="6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
@@ -6565,7 +6602,7 @@
       <c r="AH106" s="7"/>
       <c r="AI106" s="5">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AK106" s="2"/>
       <c r="AL106" s="2"/>
@@ -6575,13 +6612,13 @@
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C107" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -6616,7 +6653,7 @@
       <c r="AH107" s="7"/>
       <c r="AI107" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK107" s="2"/>
       <c r="AL107" s="2"/>
@@ -6626,13 +6663,13 @@
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C108" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
@@ -6667,7 +6704,7 @@
       <c r="AH108" s="7"/>
       <c r="AI108" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK108" s="2"/>
       <c r="AL108" s="2"/>
@@ -6677,13 +6714,13 @@
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C109" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
@@ -6718,7 +6755,7 @@
       <c r="AH109" s="7"/>
       <c r="AI109" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK109" s="2"/>
       <c r="AL109" s="2"/>
@@ -6728,13 +6765,13 @@
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
@@ -6769,7 +6806,7 @@
       <c r="AH110" s="7"/>
       <c r="AI110" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK110" s="2"/>
       <c r="AL110" s="2"/>
@@ -6779,10 +6816,10 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C111" s="6">
         <v>1</v>
@@ -6830,13 +6867,13 @@
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C112" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
@@ -6871,7 +6908,7 @@
       <c r="AH112" s="7"/>
       <c r="AI112" s="5">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK112" s="2"/>
       <c r="AL112" s="2"/>
@@ -6881,13 +6918,13 @@
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C113" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
@@ -6922,7 +6959,7 @@
       <c r="AH113" s="7"/>
       <c r="AI113" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AK113" s="2"/>
       <c r="AL113" s="2"/>
@@ -6932,13 +6969,13 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
@@ -6973,7 +7010,7 @@
       <c r="AH114" s="7"/>
       <c r="AI114" s="5">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK114" s="2"/>
       <c r="AL114" s="2"/>
@@ -6983,10 +7020,10 @@
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C115" s="6">
         <v>1</v>
@@ -7034,10 +7071,10 @@
     </row>
     <row r="116" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C116" s="6">
         <v>1</v>
@@ -7085,13 +7122,13 @@
     </row>
     <row r="117" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C117" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
@@ -7126,7 +7163,7 @@
       <c r="AH117" s="7"/>
       <c r="AI117" s="5">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK117" s="2"/>
       <c r="AL117" s="2"/>
@@ -7136,13 +7173,13 @@
     </row>
     <row r="118" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C118" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
@@ -7177,7 +7214,7 @@
       <c r="AH118" s="7"/>
       <c r="AI118" s="5">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK118" s="2"/>
       <c r="AL118" s="2"/>
@@ -7186,149 +7223,160 @@
       <c r="AO118" s="2"/>
     </row>
     <row r="119" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A119" s="34">
+      <c r="A119" s="5">
+        <v>31</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C119" s="6">
+        <v>3</v>
+      </c>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7">
+        <v>1</v>
+      </c>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7"/>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7"/>
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+      <c r="U119" s="7"/>
+      <c r="V119" s="7"/>
+      <c r="W119" s="7"/>
+      <c r="X119" s="7"/>
+      <c r="Y119" s="7"/>
+      <c r="Z119" s="7"/>
+      <c r="AA119" s="7"/>
+      <c r="AB119" s="7"/>
+      <c r="AC119" s="7"/>
+      <c r="AD119" s="7"/>
+      <c r="AE119" s="7"/>
+      <c r="AF119" s="7"/>
+      <c r="AG119" s="7"/>
+      <c r="AH119" s="7"/>
+      <c r="AI119" s="5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AK119" s="2"/>
+      <c r="AL119" s="2"/>
+      <c r="AM119" s="2"/>
+      <c r="AN119" s="2"/>
+      <c r="AO119" s="2"/>
+    </row>
+    <row r="120" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A120" s="34">
         <v>32</v>
       </c>
-      <c r="B119" s="35" t="s">
+      <c r="B120" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C119" s="36">
+      <c r="C120" s="36">
         <v>5</v>
       </c>
-      <c r="D119" s="37"/>
-      <c r="E119" s="37"/>
-      <c r="F119" s="37"/>
-      <c r="G119" s="37"/>
-      <c r="H119" s="37"/>
-      <c r="I119" s="37"/>
-      <c r="J119" s="37"/>
-      <c r="K119" s="37"/>
-      <c r="L119" s="37"/>
-      <c r="M119" s="37"/>
-      <c r="N119" s="37"/>
-      <c r="O119" s="37"/>
-      <c r="P119" s="37"/>
-      <c r="Q119" s="37"/>
-      <c r="R119" s="37"/>
-      <c r="S119" s="37"/>
-      <c r="T119" s="37"/>
-      <c r="U119" s="37"/>
-      <c r="V119" s="37"/>
-      <c r="W119" s="37"/>
-      <c r="X119" s="37"/>
-      <c r="Y119" s="37"/>
-      <c r="Z119" s="37"/>
-      <c r="AA119" s="37"/>
-      <c r="AB119" s="37"/>
-      <c r="AC119" s="37"/>
-      <c r="AD119" s="37"/>
-      <c r="AE119" s="37"/>
-      <c r="AF119" s="37"/>
-      <c r="AG119" s="37"/>
-      <c r="AH119" s="37"/>
-      <c r="AI119" s="34">
+      <c r="D120" s="37"/>
+      <c r="E120" s="37"/>
+      <c r="F120" s="37"/>
+      <c r="G120" s="37"/>
+      <c r="H120" s="37"/>
+      <c r="I120" s="37"/>
+      <c r="J120" s="37"/>
+      <c r="K120" s="37"/>
+      <c r="L120" s="37"/>
+      <c r="M120" s="37"/>
+      <c r="N120" s="37"/>
+      <c r="O120" s="37"/>
+      <c r="P120" s="37"/>
+      <c r="Q120" s="37"/>
+      <c r="R120" s="37"/>
+      <c r="S120" s="37"/>
+      <c r="T120" s="37"/>
+      <c r="U120" s="37"/>
+      <c r="V120" s="37"/>
+      <c r="W120" s="37"/>
+      <c r="X120" s="37"/>
+      <c r="Y120" s="37"/>
+      <c r="Z120" s="37"/>
+      <c r="AA120" s="37"/>
+      <c r="AB120" s="37"/>
+      <c r="AC120" s="37"/>
+      <c r="AD120" s="37"/>
+      <c r="AE120" s="37"/>
+      <c r="AF120" s="37"/>
+      <c r="AG120" s="37"/>
+      <c r="AH120" s="37"/>
+      <c r="AI120" s="34">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="AK119" s="35"/>
-      <c r="AL119" s="35"/>
-      <c r="AM119" s="35"/>
-      <c r="AN119" s="35"/>
-      <c r="AO119" s="35"/>
-    </row>
-    <row r="120" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
+      <c r="AK120" s="35"/>
+      <c r="AL120" s="35"/>
+      <c r="AM120" s="35"/>
+      <c r="AN120" s="35"/>
+      <c r="AO120" s="35"/>
+    </row>
+    <row r="121" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A121" s="5">
         <v>33</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B121" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C121" s="6">
         <v>2</v>
       </c>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="7"/>
-      <c r="S120" s="7"/>
-      <c r="T120" s="7"/>
-      <c r="U120" s="7"/>
-      <c r="V120" s="7"/>
-      <c r="W120" s="7"/>
-      <c r="X120" s="7"/>
-      <c r="Y120" s="7"/>
-      <c r="Z120" s="7"/>
-      <c r="AA120" s="7"/>
-      <c r="AB120" s="7"/>
-      <c r="AC120" s="7"/>
-      <c r="AD120" s="7"/>
-      <c r="AE120" s="7"/>
-      <c r="AF120" s="7"/>
-      <c r="AG120" s="7"/>
-      <c r="AH120" s="7"/>
-      <c r="AI120" s="5">
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="G121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="J121" s="7"/>
+      <c r="K121" s="7"/>
+      <c r="L121" s="7"/>
+      <c r="M121" s="7"/>
+      <c r="N121" s="7"/>
+      <c r="O121" s="7"/>
+      <c r="P121" s="7"/>
+      <c r="Q121" s="7"/>
+      <c r="R121" s="7"/>
+      <c r="S121" s="7"/>
+      <c r="T121" s="7"/>
+      <c r="U121" s="7"/>
+      <c r="V121" s="7"/>
+      <c r="W121" s="7"/>
+      <c r="X121" s="7"/>
+      <c r="Y121" s="7"/>
+      <c r="Z121" s="7"/>
+      <c r="AA121" s="7"/>
+      <c r="AB121" s="7"/>
+      <c r="AC121" s="7"/>
+      <c r="AD121" s="7"/>
+      <c r="AE121" s="7"/>
+      <c r="AF121" s="7"/>
+      <c r="AG121" s="7"/>
+      <c r="AH121" s="7"/>
+      <c r="AI121" s="5">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="AJ120" s="2"/>
-      <c r="AK120" s="2"/>
-      <c r="AL120" s="2"/>
-      <c r="AM120" s="2"/>
-      <c r="AN120" s="2"/>
-      <c r="AO120" s="2"/>
-    </row>
-    <row r="121" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12"/>
-      <c r="C121" s="16"/>
-      <c r="D121" s="17"/>
-      <c r="E121" s="17"/>
-      <c r="F121" s="17"/>
-      <c r="G121" s="17"/>
-      <c r="H121" s="17"/>
-      <c r="I121" s="17"/>
-      <c r="J121" s="17"/>
-      <c r="K121" s="17"/>
-      <c r="L121" s="17"/>
-      <c r="M121" s="17"/>
-      <c r="N121" s="17"/>
-      <c r="O121" s="17"/>
-      <c r="P121" s="17"/>
-      <c r="Q121" s="17"/>
-      <c r="R121" s="17"/>
-      <c r="S121" s="17"/>
-      <c r="T121" s="17"/>
-      <c r="U121" s="17"/>
-      <c r="V121" s="17"/>
-      <c r="W121" s="17"/>
-      <c r="X121" s="17"/>
-      <c r="Y121" s="17"/>
-      <c r="Z121" s="17"/>
-      <c r="AA121" s="17"/>
-      <c r="AB121" s="17"/>
-      <c r="AC121" s="17"/>
-      <c r="AD121" s="17"/>
-      <c r="AE121" s="17"/>
-      <c r="AF121" s="17"/>
-      <c r="AG121" s="17"/>
-      <c r="AH121" s="17"/>
-      <c r="AI121" s="12"/>
-      <c r="AK121" s="12"/>
-      <c r="AL121" s="12"/>
-      <c r="AM121" s="12"/>
-      <c r="AN121" s="12"/>
-      <c r="AO121" s="12"/>
+      <c r="AJ121" s="2"/>
+      <c r="AK121" s="2"/>
+      <c r="AL121" s="2"/>
+      <c r="AM121" s="2"/>
+      <c r="AN121" s="2"/>
+      <c r="AO121" s="2"/>
     </row>
     <row r="122" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A122" s="12"/>
@@ -7456,187 +7504,178 @@
       <c r="AN124" s="12"/>
       <c r="AO124" s="12"/>
     </row>
-    <row r="128" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A128" s="42" t="s">
+    <row r="125" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A125" s="12"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="16"/>
+      <c r="D125" s="17"/>
+      <c r="E125" s="17"/>
+      <c r="F125" s="17"/>
+      <c r="G125" s="17"/>
+      <c r="H125" s="17"/>
+      <c r="I125" s="17"/>
+      <c r="J125" s="17"/>
+      <c r="K125" s="17"/>
+      <c r="L125" s="17"/>
+      <c r="M125" s="17"/>
+      <c r="N125" s="17"/>
+      <c r="O125" s="17"/>
+      <c r="P125" s="17"/>
+      <c r="Q125" s="17"/>
+      <c r="R125" s="17"/>
+      <c r="S125" s="17"/>
+      <c r="T125" s="17"/>
+      <c r="U125" s="17"/>
+      <c r="V125" s="17"/>
+      <c r="W125" s="17"/>
+      <c r="X125" s="17"/>
+      <c r="Y125" s="17"/>
+      <c r="Z125" s="17"/>
+      <c r="AA125" s="17"/>
+      <c r="AB125" s="17"/>
+      <c r="AC125" s="17"/>
+      <c r="AD125" s="17"/>
+      <c r="AE125" s="17"/>
+      <c r="AF125" s="17"/>
+      <c r="AG125" s="17"/>
+      <c r="AH125" s="17"/>
+      <c r="AI125" s="12"/>
+      <c r="AK125" s="12"/>
+      <c r="AL125" s="12"/>
+      <c r="AM125" s="12"/>
+      <c r="AN125" s="12"/>
+      <c r="AO125" s="12"/>
+    </row>
+    <row r="129" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A129" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="B128" s="42"/>
-      <c r="AI128" s="12"/>
-    </row>
-    <row r="129" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A129" s="13" t="s">
+      <c r="B129" s="44"/>
+      <c r="AI129" s="12"/>
+    </row>
+    <row r="130" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A130" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B130" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C129" s="14" t="s">
+      <c r="C130" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D129" s="14">
+      <c r="D130" s="14">
         <v>1</v>
       </c>
-      <c r="E129" s="14">
+      <c r="E130" s="14">
         <v>2</v>
       </c>
-      <c r="F129" s="14">
+      <c r="F130" s="14">
         <v>3</v>
       </c>
-      <c r="G129" s="14">
+      <c r="G130" s="14">
         <v>4</v>
       </c>
-      <c r="H129" s="14">
+      <c r="H130" s="14">
         <v>5</v>
       </c>
-      <c r="I129" s="14">
+      <c r="I130" s="14">
         <v>6</v>
       </c>
-      <c r="J129" s="14">
+      <c r="J130" s="14">
         <v>7</v>
       </c>
-      <c r="K129" s="14">
+      <c r="K130" s="14">
         <v>8</v>
       </c>
-      <c r="L129" s="14">
+      <c r="L130" s="14">
         <v>9</v>
       </c>
-      <c r="M129" s="14">
+      <c r="M130" s="14">
         <v>10</v>
       </c>
-      <c r="N129" s="14">
+      <c r="N130" s="14">
         <v>11</v>
       </c>
-      <c r="O129" s="14">
+      <c r="O130" s="14">
         <v>12</v>
       </c>
-      <c r="P129" s="14">
+      <c r="P130" s="14">
         <v>13</v>
       </c>
-      <c r="Q129" s="14">
+      <c r="Q130" s="14">
         <v>14</v>
       </c>
-      <c r="R129" s="14">
+      <c r="R130" s="14">
         <v>15</v>
       </c>
-      <c r="S129" s="14">
+      <c r="S130" s="14">
         <v>16</v>
       </c>
-      <c r="T129" s="14">
+      <c r="T130" s="14">
         <v>17</v>
       </c>
-      <c r="U129" s="14">
+      <c r="U130" s="14">
         <v>18</v>
       </c>
-      <c r="V129" s="14">
+      <c r="V130" s="14">
         <v>19</v>
       </c>
-      <c r="W129" s="14">
+      <c r="W130" s="14">
         <v>20</v>
       </c>
-      <c r="X129" s="14">
+      <c r="X130" s="14">
         <v>21</v>
       </c>
-      <c r="Y129" s="14">
+      <c r="Y130" s="14">
         <v>22</v>
       </c>
-      <c r="Z129" s="14">
+      <c r="Z130" s="14">
         <v>23</v>
       </c>
-      <c r="AA129" s="14">
+      <c r="AA130" s="14">
         <v>24</v>
       </c>
-      <c r="AB129" s="14">
+      <c r="AB130" s="14">
         <v>25</v>
       </c>
-      <c r="AC129" s="14">
+      <c r="AC130" s="14">
         <v>26</v>
       </c>
-      <c r="AD129" s="14">
+      <c r="AD130" s="14">
         <v>27</v>
       </c>
-      <c r="AE129" s="14">
+      <c r="AE130" s="14">
         <v>28</v>
       </c>
-      <c r="AF129" s="14">
+      <c r="AF130" s="14">
         <v>29</v>
       </c>
-      <c r="AG129" s="14">
+      <c r="AG130" s="14">
         <v>30</v>
       </c>
-      <c r="AH129" s="14">
+      <c r="AH130" s="14">
         <v>31</v>
       </c>
-      <c r="AI129" s="15" t="s">
+      <c r="AI130" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="AK129" s="38" t="s">
+      <c r="AK130" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AL129" s="39"/>
-      <c r="AM129" s="39"/>
-      <c r="AN129" s="39"/>
-      <c r="AO129" s="40"/>
-    </row>
-    <row r="130" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A130" s="6">
-        <v>1</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C130" s="6">
-        <v>3</v>
-      </c>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
-      <c r="K130" s="7"/>
-      <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="7"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="7"/>
-      <c r="S130" s="7"/>
-      <c r="T130" s="7"/>
-      <c r="U130" s="7"/>
-      <c r="V130" s="7"/>
-      <c r="W130" s="7"/>
-      <c r="X130" s="7"/>
-      <c r="Y130" s="7"/>
-      <c r="Z130" s="7"/>
-      <c r="AA130" s="7"/>
-      <c r="AB130" s="7"/>
-      <c r="AC130" s="7"/>
-      <c r="AD130" s="7"/>
-      <c r="AE130" s="7"/>
-      <c r="AF130" s="7"/>
-      <c r="AG130" s="7"/>
-      <c r="AH130" s="7"/>
-      <c r="AI130" s="6">
-        <f>C130-D130-E130-F130-G130-H130-I130-J130-K130-L130-M130-N130-O130-P130-Q130-R130-S130-T130-U130-V130-W130-X130-Y130-Z130-AA130-AB130-AC130-AD130-AE130-AF130-AG130-AH130</f>
-        <v>3</v>
-      </c>
-      <c r="AK130" s="2"/>
-      <c r="AL130" s="2"/>
-      <c r="AM130" s="2"/>
-      <c r="AN130" s="2"/>
-      <c r="AO130" s="2"/>
+      <c r="AL130" s="40"/>
+      <c r="AM130" s="40"/>
+      <c r="AN130" s="40"/>
+      <c r="AO130" s="41"/>
     </row>
     <row r="131" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C131" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -7670,8 +7709,8 @@
       <c r="AG131" s="7"/>
       <c r="AH131" s="7"/>
       <c r="AI131" s="6">
-        <f t="shared" ref="AI131:AI175" si="4">C131-D131-E131-F131-G131-H131-I131-J131-K131-L131-M131-N131-O131-P131-Q131-R131-S131-T131-U131-V131-W131-X131-Y131-Z131-AA131-AB131-AC131-AD131-AE131-AF131-AG131-AH131</f>
-        <v>1</v>
+        <f>C131-D131-E131-F131-G131-H131-I131-J131-K131-L131-M131-N131-O131-P131-Q131-R131-S131-T131-U131-V131-W131-X131-Y131-Z131-AA131-AB131-AC131-AD131-AE131-AF131-AG131-AH131</f>
+        <v>3</v>
       </c>
       <c r="AK131" s="2"/>
       <c r="AL131" s="2"/>
@@ -7681,12 +7720,12 @@
     </row>
     <row r="132" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C132" s="3">
+        <v>100</v>
+      </c>
+      <c r="C132" s="6">
         <v>1</v>
       </c>
       <c r="D132" s="7"/>
@@ -7721,7 +7760,7 @@
       <c r="AG132" s="7"/>
       <c r="AH132" s="7"/>
       <c r="AI132" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AI132:AI176" si="4">C132-D132-E132-F132-G132-H132-I132-J132-K132-L132-M132-N132-O132-P132-Q132-R132-S132-T132-U132-V132-W132-X132-Y132-Z132-AA132-AB132-AC132-AD132-AE132-AF132-AG132-AH132</f>
         <v>1</v>
       </c>
       <c r="AK132" s="2"/>
@@ -7732,10 +7771,10 @@
     </row>
     <row r="133" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C133" s="3">
         <v>1</v>
@@ -7783,13 +7822,13 @@
     </row>
     <row r="134" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C134" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -7824,7 +7863,7 @@
       <c r="AH134" s="7"/>
       <c r="AI134" s="6">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AK134" s="2"/>
       <c r="AL134" s="2"/>
@@ -7834,13 +7873,13 @@
     </row>
     <row r="135" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C135" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -7875,7 +7914,7 @@
       <c r="AH135" s="7"/>
       <c r="AI135" s="6">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AK135" s="2"/>
       <c r="AL135" s="2"/>
@@ -7885,10 +7924,10 @@
     </row>
     <row r="136" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C136" s="3">
         <v>5</v>
@@ -7936,13 +7975,13 @@
     </row>
     <row r="137" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C137" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -7977,7 +8016,7 @@
       <c r="AH137" s="7"/>
       <c r="AI137" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK137" s="2"/>
       <c r="AL137" s="2"/>
@@ -7987,13 +8026,13 @@
     </row>
     <row r="138" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C138" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -8028,7 +8067,7 @@
       <c r="AH138" s="7"/>
       <c r="AI138" s="6">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK138" s="2"/>
       <c r="AL138" s="2"/>
@@ -8038,10 +8077,10 @@
     </row>
     <row r="139" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C139" s="3">
         <v>1</v>
@@ -8089,10 +8128,10 @@
     </row>
     <row r="140" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C140" s="3">
         <v>1</v>
@@ -8140,10 +8179,10 @@
     </row>
     <row r="141" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C141" s="3">
         <v>1</v>
@@ -8191,10 +8230,10 @@
     </row>
     <row r="142" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C142" s="3">
         <v>1</v>
@@ -8242,10 +8281,10 @@
     </row>
     <row r="143" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C143" s="3">
         <v>1</v>
@@ -8293,10 +8332,10 @@
     </row>
     <row r="144" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C144" s="3">
         <v>1</v>
@@ -8344,10 +8383,10 @@
     </row>
     <row r="145" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C145" s="3">
         <v>1</v>
@@ -8395,13 +8434,13 @@
     </row>
     <row r="146" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C146" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
@@ -8436,7 +8475,7 @@
       <c r="AH146" s="7"/>
       <c r="AI146" s="6">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="AK146" s="2"/>
       <c r="AL146" s="2"/>
@@ -8446,13 +8485,13 @@
     </row>
     <row r="147" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C147" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
@@ -8487,7 +8526,7 @@
       <c r="AH147" s="7"/>
       <c r="AI147" s="6">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AK147" s="2"/>
       <c r="AL147" s="2"/>
@@ -8497,13 +8536,13 @@
     </row>
     <row r="148" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C148" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
@@ -8538,7 +8577,7 @@
       <c r="AH148" s="7"/>
       <c r="AI148" s="6">
         <f t="shared" si="4"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AK148" s="2"/>
       <c r="AL148" s="2"/>
@@ -8548,13 +8587,13 @@
     </row>
     <row r="149" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C149" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
@@ -8589,7 +8628,7 @@
       <c r="AH149" s="7"/>
       <c r="AI149" s="6">
         <f t="shared" si="4"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AK149" s="2"/>
       <c r="AL149" s="2"/>
@@ -8599,13 +8638,13 @@
     </row>
     <row r="150" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C150" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
@@ -8640,7 +8679,7 @@
       <c r="AH150" s="7"/>
       <c r="AI150" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="AK150" s="2"/>
       <c r="AL150" s="2"/>
@@ -8650,13 +8689,13 @@
     </row>
     <row r="151" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C151" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
@@ -8691,7 +8730,7 @@
       <c r="AH151" s="7"/>
       <c r="AI151" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK151" s="2"/>
       <c r="AL151" s="2"/>
@@ -8701,10 +8740,10 @@
     </row>
     <row r="152" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C152" s="3">
         <v>2</v>
@@ -8752,10 +8791,10 @@
     </row>
     <row r="153" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C153" s="3">
         <v>2</v>
@@ -8803,13 +8842,13 @@
     </row>
     <row r="154" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C154" s="6">
-        <v>31</v>
+        <v>122</v>
+      </c>
+      <c r="C154" s="3">
+        <v>2</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
@@ -8844,7 +8883,7 @@
       <c r="AH154" s="7"/>
       <c r="AI154" s="6">
         <f t="shared" si="4"/>
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="AK154" s="2"/>
       <c r="AL154" s="2"/>
@@ -8854,10 +8893,10 @@
     </row>
     <row r="155" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C155" s="6">
         <v>31</v>
@@ -8905,13 +8944,13 @@
     </row>
     <row r="156" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C156" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
@@ -8946,7 +8985,7 @@
       <c r="AH156" s="7"/>
       <c r="AI156" s="6">
         <f t="shared" si="4"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AK156" s="2"/>
       <c r="AL156" s="2"/>
@@ -8956,13 +8995,13 @@
     </row>
     <row r="157" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
+        <v>28</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C157" s="6">
         <v>29</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C157" s="6">
-        <v>30</v>
       </c>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
@@ -8997,7 +9036,7 @@
       <c r="AH157" s="7"/>
       <c r="AI157" s="6">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK157" s="2"/>
       <c r="AL157" s="2"/>
@@ -9007,13 +9046,13 @@
     </row>
     <row r="158" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
+        <v>29</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C158" s="6">
         <v>30</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C158" s="6">
-        <v>2</v>
       </c>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
@@ -9048,7 +9087,7 @@
       <c r="AH158" s="7"/>
       <c r="AI158" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="AK158" s="2"/>
       <c r="AL158" s="2"/>
@@ -9058,13 +9097,13 @@
     </row>
     <row r="159" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C159" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
@@ -9099,7 +9138,7 @@
       <c r="AH159" s="7"/>
       <c r="AI159" s="6">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK159" s="2"/>
       <c r="AL159" s="2"/>
@@ -9109,10 +9148,10 @@
     </row>
     <row r="160" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C160" s="6">
         <v>4</v>
@@ -9160,10 +9199,10 @@
     </row>
     <row r="161" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C161" s="6">
         <v>4</v>
@@ -9211,13 +9250,13 @@
     </row>
     <row r="162" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C162" s="6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
@@ -9252,7 +9291,7 @@
       <c r="AH162" s="7"/>
       <c r="AI162" s="6">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AK162" s="2"/>
       <c r="AL162" s="2"/>
@@ -9262,13 +9301,13 @@
     </row>
     <row r="163" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C163" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
@@ -9303,7 +9342,7 @@
       <c r="AH163" s="7"/>
       <c r="AI163" s="6">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AK163" s="2"/>
       <c r="AL163" s="2"/>
@@ -9313,10 +9352,10 @@
     </row>
     <row r="164" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C164" s="6">
         <v>11</v>
@@ -9364,10 +9403,10 @@
     </row>
     <row r="165" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C165" s="6">
         <v>11</v>
@@ -9415,13 +9454,13 @@
     </row>
     <row r="166" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C166" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
@@ -9456,7 +9495,7 @@
       <c r="AH166" s="7"/>
       <c r="AI166" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AK166" s="2"/>
       <c r="AL166" s="2"/>
@@ -9466,13 +9505,13 @@
     </row>
     <row r="167" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C167" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
@@ -9507,7 +9546,7 @@
       <c r="AH167" s="7"/>
       <c r="AI167" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK167" s="2"/>
       <c r="AL167" s="2"/>
@@ -9517,10 +9556,10 @@
     </row>
     <row r="168" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C168" s="6">
         <v>3</v>
@@ -9568,13 +9607,13 @@
     </row>
     <row r="169" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C169" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
@@ -9609,7 +9648,7 @@
       <c r="AH169" s="7"/>
       <c r="AI169" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK169" s="2"/>
       <c r="AL169" s="2"/>
@@ -9619,13 +9658,13 @@
     </row>
     <row r="170" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
-        <v>42</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>139</v>
+        <v>41</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="C170" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
@@ -9660,7 +9699,7 @@
       <c r="AH170" s="7"/>
       <c r="AI170" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK170" s="2"/>
       <c r="AL170" s="2"/>
@@ -9670,10 +9709,10 @@
     </row>
     <row r="171" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C171" s="6">
         <v>3</v>
@@ -9721,13 +9760,13 @@
     </row>
     <row r="172" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C172" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
@@ -9762,7 +9801,7 @@
       <c r="AH172" s="7"/>
       <c r="AI172" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK172" s="2"/>
       <c r="AL172" s="2"/>
@@ -9772,13 +9811,13 @@
     </row>
     <row r="173" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C173" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
@@ -9813,7 +9852,7 @@
       <c r="AH173" s="7"/>
       <c r="AI173" s="6">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AK173" s="2"/>
       <c r="AL173" s="2"/>
@@ -9823,13 +9862,13 @@
     </row>
     <row r="174" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C174" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
@@ -9864,7 +9903,7 @@
       <c r="AH174" s="7"/>
       <c r="AI174" s="6">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AK174" s="2"/>
       <c r="AL174" s="2"/>
@@ -9874,13 +9913,13 @@
     </row>
     <row r="175" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C175" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
@@ -9915,7 +9954,7 @@
       <c r="AH175" s="7"/>
       <c r="AI175" s="6">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK175" s="2"/>
       <c r="AL175" s="2"/>
@@ -9924,46 +9963,55 @@
       <c r="AO175" s="2"/>
     </row>
     <row r="176" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A176" s="12"/>
-      <c r="B176" s="12"/>
-      <c r="C176" s="16"/>
-      <c r="D176" s="17"/>
-      <c r="E176" s="17"/>
-      <c r="F176" s="17"/>
-      <c r="G176" s="17"/>
-      <c r="H176" s="17"/>
-      <c r="I176" s="17"/>
-      <c r="J176" s="17"/>
-      <c r="K176" s="17"/>
-      <c r="L176" s="17"/>
-      <c r="M176" s="17"/>
-      <c r="N176" s="17"/>
-      <c r="O176" s="17"/>
-      <c r="P176" s="17"/>
-      <c r="Q176" s="17"/>
-      <c r="R176" s="17"/>
-      <c r="S176" s="17"/>
-      <c r="T176" s="17"/>
-      <c r="U176" s="17"/>
-      <c r="V176" s="17"/>
-      <c r="W176" s="17"/>
-      <c r="X176" s="17"/>
-      <c r="Y176" s="17"/>
-      <c r="Z176" s="17"/>
-      <c r="AA176" s="17"/>
-      <c r="AB176" s="17"/>
-      <c r="AC176" s="17"/>
-      <c r="AD176" s="17"/>
-      <c r="AE176" s="17"/>
-      <c r="AF176" s="17"/>
-      <c r="AG176" s="17"/>
-      <c r="AH176" s="17"/>
-      <c r="AI176" s="12"/>
-      <c r="AK176" s="12"/>
-      <c r="AL176" s="12"/>
-      <c r="AM176" s="12"/>
-      <c r="AN176" s="12"/>
-      <c r="AO176" s="12"/>
+      <c r="A176" s="6">
+        <v>47</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C176" s="6">
+        <v>3</v>
+      </c>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="7"/>
+      <c r="G176" s="7"/>
+      <c r="H176" s="7"/>
+      <c r="I176" s="7"/>
+      <c r="J176" s="7"/>
+      <c r="K176" s="7"/>
+      <c r="L176" s="7"/>
+      <c r="M176" s="7"/>
+      <c r="N176" s="7"/>
+      <c r="O176" s="7"/>
+      <c r="P176" s="7"/>
+      <c r="Q176" s="7"/>
+      <c r="R176" s="7"/>
+      <c r="S176" s="7"/>
+      <c r="T176" s="7"/>
+      <c r="U176" s="7"/>
+      <c r="V176" s="7"/>
+      <c r="W176" s="7"/>
+      <c r="X176" s="7"/>
+      <c r="Y176" s="7"/>
+      <c r="Z176" s="7"/>
+      <c r="AA176" s="7"/>
+      <c r="AB176" s="7"/>
+      <c r="AC176" s="7"/>
+      <c r="AD176" s="7"/>
+      <c r="AE176" s="7"/>
+      <c r="AF176" s="7"/>
+      <c r="AG176" s="7"/>
+      <c r="AH176" s="7"/>
+      <c r="AI176" s="6">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AK176" s="2"/>
+      <c r="AL176" s="2"/>
+      <c r="AM176" s="2"/>
+      <c r="AN176" s="2"/>
+      <c r="AO176" s="2"/>
     </row>
     <row r="177" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A177" s="12"/>
@@ -10091,169 +10139,171 @@
       <c r="AN179" s="12"/>
       <c r="AO179" s="12"/>
     </row>
-    <row r="181" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A181" s="43" t="s">
+    <row r="180" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A180" s="12"/>
+      <c r="B180" s="12"/>
+      <c r="C180" s="16"/>
+      <c r="D180" s="17"/>
+      <c r="E180" s="17"/>
+      <c r="F180" s="17"/>
+      <c r="G180" s="17"/>
+      <c r="H180" s="17"/>
+      <c r="I180" s="17"/>
+      <c r="J180" s="17"/>
+      <c r="K180" s="17"/>
+      <c r="L180" s="17"/>
+      <c r="M180" s="17"/>
+      <c r="N180" s="17"/>
+      <c r="O180" s="17"/>
+      <c r="P180" s="17"/>
+      <c r="Q180" s="17"/>
+      <c r="R180" s="17"/>
+      <c r="S180" s="17"/>
+      <c r="T180" s="17"/>
+      <c r="U180" s="17"/>
+      <c r="V180" s="17"/>
+      <c r="W180" s="17"/>
+      <c r="X180" s="17"/>
+      <c r="Y180" s="17"/>
+      <c r="Z180" s="17"/>
+      <c r="AA180" s="17"/>
+      <c r="AB180" s="17"/>
+      <c r="AC180" s="17"/>
+      <c r="AD180" s="17"/>
+      <c r="AE180" s="17"/>
+      <c r="AF180" s="17"/>
+      <c r="AG180" s="17"/>
+      <c r="AH180" s="17"/>
+      <c r="AI180" s="12"/>
+      <c r="AK180" s="12"/>
+      <c r="AL180" s="12"/>
+      <c r="AM180" s="12"/>
+      <c r="AN180" s="12"/>
+      <c r="AO180" s="12"/>
+    </row>
+    <row r="182" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A182" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="B181" s="43"/>
-    </row>
-    <row r="182" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A182" s="13" t="s">
+      <c r="B182" s="42"/>
+    </row>
+    <row r="183" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A183" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="B183" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C182" s="15" t="s">
+      <c r="C183" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D182" s="14">
+      <c r="D183" s="14">
         <v>1</v>
       </c>
-      <c r="E182" s="14">
+      <c r="E183" s="14">
         <v>2</v>
       </c>
-      <c r="F182" s="14">
+      <c r="F183" s="14">
         <v>3</v>
       </c>
-      <c r="G182" s="14">
+      <c r="G183" s="14">
         <v>4</v>
       </c>
-      <c r="H182" s="14">
+      <c r="H183" s="14">
         <v>5</v>
       </c>
-      <c r="I182" s="14">
+      <c r="I183" s="14">
         <v>6</v>
       </c>
-      <c r="J182" s="14">
+      <c r="J183" s="14">
         <v>7</v>
       </c>
-      <c r="K182" s="14">
+      <c r="K183" s="14">
         <v>8</v>
       </c>
-      <c r="L182" s="14">
+      <c r="L183" s="14">
         <v>9</v>
       </c>
-      <c r="M182" s="14">
+      <c r="M183" s="14">
         <v>10</v>
       </c>
-      <c r="N182" s="14">
+      <c r="N183" s="14">
         <v>11</v>
       </c>
-      <c r="O182" s="14">
+      <c r="O183" s="14">
         <v>12</v>
       </c>
-      <c r="P182" s="14">
+      <c r="P183" s="14">
         <v>13</v>
       </c>
-      <c r="Q182" s="14">
+      <c r="Q183" s="14">
         <v>14</v>
       </c>
-      <c r="R182" s="14">
+      <c r="R183" s="14">
         <v>15</v>
       </c>
-      <c r="S182" s="14">
+      <c r="S183" s="14">
         <v>16</v>
       </c>
-      <c r="T182" s="14">
+      <c r="T183" s="14">
         <v>17</v>
       </c>
-      <c r="U182" s="14">
+      <c r="U183" s="14">
         <v>18</v>
       </c>
-      <c r="V182" s="14">
+      <c r="V183" s="14">
         <v>19</v>
       </c>
-      <c r="W182" s="14">
+      <c r="W183" s="14">
         <v>20</v>
       </c>
-      <c r="X182" s="14">
+      <c r="X183" s="14">
         <v>21</v>
       </c>
-      <c r="Y182" s="14">
+      <c r="Y183" s="14">
         <v>22</v>
       </c>
-      <c r="Z182" s="14">
+      <c r="Z183" s="14">
         <v>23</v>
       </c>
-      <c r="AA182" s="14">
+      <c r="AA183" s="14">
         <v>24</v>
       </c>
-      <c r="AB182" s="14">
+      <c r="AB183" s="14">
         <v>25</v>
       </c>
-      <c r="AC182" s="14">
+      <c r="AC183" s="14">
         <v>26</v>
       </c>
-      <c r="AD182" s="14">
+      <c r="AD183" s="14">
         <v>27</v>
       </c>
-      <c r="AE182" s="14">
+      <c r="AE183" s="14">
         <v>28</v>
       </c>
-      <c r="AF182" s="14">
+      <c r="AF183" s="14">
         <v>29</v>
       </c>
-      <c r="AG182" s="14">
+      <c r="AG183" s="14">
         <v>30</v>
       </c>
-      <c r="AH182" s="14">
+      <c r="AH183" s="14">
         <v>31</v>
       </c>
-      <c r="AI182" s="15" t="s">
+      <c r="AI183" s="15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
+    <row r="184" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
         <v>1</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B184" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C183" s="6">
+      <c r="C184" s="6">
         <v>1</v>
       </c>
-      <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
-      <c r="F183" s="7"/>
-      <c r="G183" s="7"/>
-      <c r="H183" s="7"/>
-      <c r="I183" s="7"/>
-      <c r="J183" s="7"/>
-      <c r="K183" s="7"/>
-      <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
-      <c r="N183" s="7"/>
-      <c r="O183" s="7"/>
-      <c r="P183" s="7"/>
-      <c r="Q183" s="7"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="7"/>
-      <c r="T183" s="7"/>
-      <c r="U183" s="7"/>
-      <c r="V183" s="7"/>
-      <c r="W183" s="7"/>
-      <c r="X183" s="7"/>
-      <c r="Y183" s="7"/>
-      <c r="Z183" s="7"/>
-      <c r="AA183" s="7"/>
-      <c r="AB183" s="7"/>
-      <c r="AC183" s="7"/>
-      <c r="AD183" s="7"/>
-      <c r="AE183" s="7"/>
-      <c r="AF183" s="7"/>
-      <c r="AG183" s="7"/>
-      <c r="AH183" s="7"/>
-      <c r="AI183" s="6">
-        <f>C183-D183-E183-F183-G183-H183-I183-J183-K183-L183-M183-N183-O183-P183-Q183-R183-S183-T183-U183-V183-W183-X183-Y183-Z183-AA183-AB183-AC183-AD183-AE183-AF183-AG183-AH183</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A184" s="6"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="6"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -10286,8 +10336,8 @@
       <c r="AG184" s="7"/>
       <c r="AH184" s="7"/>
       <c r="AI184" s="6">
-        <f t="shared" ref="AI184:AI194" si="5">C184-D184-E184-F184-G184-H184-I184-J184-K184-L184-M184-N184-O184-P184-Q184-R184-S184-T184-U184-V184-W184-X184-Y184-Z184-AA184-AB184-AC184-AD184-AE184-AF184-AG184-AH184</f>
-        <v>0</v>
+        <f>C184-D184-E184-F184-G184-H184-I184-J184-K184-L184-M184-N184-O184-P184-Q184-R184-S184-T184-U184-V184-W184-X184-Y184-Z184-AA184-AB184-AC184-AD184-AE184-AF184-AG184-AH184</f>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:41" x14ac:dyDescent="0.25">
@@ -10326,13 +10376,14 @@
       <c r="AG185" s="7"/>
       <c r="AH185" s="7"/>
       <c r="AI185" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AI185:AI195" si="5">C185-D185-E185-F185-G185-H185-I185-J185-K185-L185-M185-N185-O185-P185-Q185-R185-S185-T185-U185-V185-W185-X185-Y185-Z185-AA185-AB185-AC185-AD185-AE185-AF185-AG185-AH185</f>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
-      <c r="B186" s="2"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="6"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -10372,7 +10423,6 @@
     <row r="187" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="2"/>
-      <c r="C187" s="6"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -10689,20 +10739,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A195" s="6"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
+      <c r="K195" s="7"/>
+      <c r="L195" s="7"/>
+      <c r="M195" s="7"/>
+      <c r="N195" s="7"/>
+      <c r="O195" s="7"/>
+      <c r="P195" s="7"/>
+      <c r="Q195" s="7"/>
+      <c r="R195" s="7"/>
+      <c r="S195" s="7"/>
+      <c r="T195" s="7"/>
+      <c r="U195" s="7"/>
+      <c r="V195" s="7"/>
+      <c r="W195" s="7"/>
+      <c r="X195" s="7"/>
+      <c r="Y195" s="7"/>
+      <c r="Z195" s="7"/>
+      <c r="AA195" s="7"/>
+      <c r="AB195" s="7"/>
+      <c r="AC195" s="7"/>
+      <c r="AD195" s="7"/>
+      <c r="AE195" s="7"/>
+      <c r="AF195" s="7"/>
+      <c r="AG195" s="7"/>
+      <c r="AH195" s="7"/>
+      <c r="AI195" s="6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A181:B181"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A129:B129"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="AK129:AO129"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="AK130:AO130"/>
     <mergeCell ref="AK3:AO3"/>
-    <mergeCell ref="AK33:AO33"/>
-    <mergeCell ref="AK51:AO51"/>
-    <mergeCell ref="AK87:AO87"/>
+    <mergeCell ref="AK34:AO34"/>
+    <mergeCell ref="AK52:AO52"/>
+    <mergeCell ref="AK88:AO88"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Rekap Barang September.xlsx
+++ b/Rekap Barang September.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955CA32D-9B98-40E5-BFC8-DE20F3963606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81897DE0-229C-46B5-B55E-213238963F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F7CA82D4-8FEC-46C5-8E3D-E43D8F29F763}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{F7CA82D4-8FEC-46C5-8E3D-E43D8F29F763}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -776,6 +776,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -796,12 +802,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1151,50 +1151,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="45"/>
-      <c r="AI1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
       <c r="AJ1" s="8"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="42"/>
+      <c r="B2" s="44"/>
       <c r="AI2" s="12"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
@@ -1304,13 +1304,13 @@
         <v>3</v>
       </c>
       <c r="AJ3" s="16"/>
-      <c r="AK3" s="39" t="s">
+      <c r="AK3" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="41"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42"/>
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="43"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -2250,7 +2250,7 @@
         <v>30</v>
       </c>
       <c r="AJ21" s="16"/>
-      <c r="AK21" s="46">
+      <c r="AK21" s="39">
         <v>46151</v>
       </c>
       <c r="AL21" s="2"/>
@@ -2268,7 +2268,9 @@
       <c r="C22" s="3">
         <v>10</v>
       </c>
-      <c r="D22" s="7"/>
+      <c r="D22" s="7">
+        <v>5</v>
+      </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -2301,10 +2303,10 @@
       <c r="AH22" s="7"/>
       <c r="AI22" s="6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AJ22" s="16"/>
-      <c r="AK22" s="47"/>
+      <c r="AK22" s="40"/>
       <c r="AL22" s="2"/>
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
@@ -2356,7 +2358,7 @@
         <v>14</v>
       </c>
       <c r="AJ23" s="16"/>
-      <c r="AK23" s="46">
+      <c r="AK23" s="39">
         <v>46151</v>
       </c>
       <c r="AL23" s="2"/>
@@ -2424,7 +2426,7 @@
         <v>54</v>
       </c>
       <c r="C25" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -2459,7 +2461,7 @@
       <c r="AH25" s="7"/>
       <c r="AI25" s="6">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AJ25" s="16"/>
       <c r="AK25" s="2"/>
@@ -2779,10 +2781,10 @@
       <c r="AI32" s="12"/>
     </row>
     <row r="33" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="42"/>
+      <c r="B33" s="44"/>
     </row>
     <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
@@ -2891,13 +2893,13 @@
         <v>3</v>
       </c>
       <c r="AJ34" s="16"/>
-      <c r="AK34" s="39" t="s">
+      <c r="AK34" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="AL34" s="40"/>
-      <c r="AM34" s="40"/>
-      <c r="AN34" s="40"/>
-      <c r="AO34" s="41"/>
+      <c r="AL34" s="42"/>
+      <c r="AM34" s="42"/>
+      <c r="AN34" s="42"/>
+      <c r="AO34" s="43"/>
     </row>
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
@@ -3696,10 +3698,10 @@
       <c r="AO50" s="12"/>
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A51" s="43" t="s">
+      <c r="A51" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="43"/>
+      <c r="B51" s="45"/>
       <c r="C51" s="18"/>
       <c r="D51" s="19"/>
       <c r="E51" s="19"/>
@@ -3847,13 +3849,13 @@
         <v>3</v>
       </c>
       <c r="AJ52" s="27"/>
-      <c r="AK52" s="39" t="s">
+      <c r="AK52" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="AL52" s="40"/>
-      <c r="AM52" s="40"/>
-      <c r="AN52" s="40"/>
-      <c r="AO52" s="41"/>
+      <c r="AL52" s="42"/>
+      <c r="AM52" s="42"/>
+      <c r="AN52" s="42"/>
+      <c r="AO52" s="43"/>
     </row>
     <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" s="28">
@@ -4193,9 +4195,7 @@
         <v>2</v>
       </c>
       <c r="G59" s="30"/>
-      <c r="H59" s="30">
-        <v>9</v>
-      </c>
+      <c r="H59" s="30"/>
       <c r="I59" s="30"/>
       <c r="J59" s="30"/>
       <c r="K59" s="30"/>
@@ -4224,7 +4224,7 @@
       <c r="AH59" s="30"/>
       <c r="AI59" s="5">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="AJ59" s="27"/>
       <c r="AK59" s="2"/>
@@ -5540,10 +5540,10 @@
       <c r="AO84" s="2"/>
     </row>
     <row r="87" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A87" s="43" t="s">
+      <c r="A87" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="B87" s="43"/>
+      <c r="B87" s="45"/>
       <c r="C87" s="20"/>
       <c r="D87" s="19"/>
       <c r="E87" s="19"/>
@@ -5684,13 +5684,13 @@
       <c r="AI88" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="AK88" s="39" t="s">
+      <c r="AK88" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="AL88" s="40"/>
-      <c r="AM88" s="40"/>
-      <c r="AN88" s="40"/>
-      <c r="AO88" s="41"/>
+      <c r="AL88" s="42"/>
+      <c r="AM88" s="42"/>
+      <c r="AN88" s="42"/>
+      <c r="AO88" s="43"/>
     </row>
     <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
@@ -7547,10 +7547,10 @@
       <c r="AO125" s="12"/>
     </row>
     <row r="129" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A129" s="44" t="s">
+      <c r="A129" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="B129" s="44"/>
+      <c r="B129" s="46"/>
       <c r="AI129" s="12"/>
     </row>
     <row r="130" spans="1:41" x14ac:dyDescent="0.25">
@@ -7659,13 +7659,13 @@
       <c r="AI130" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="AK130" s="39" t="s">
+      <c r="AK130" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="AL130" s="40"/>
-      <c r="AM130" s="40"/>
-      <c r="AN130" s="40"/>
-      <c r="AO130" s="41"/>
+      <c r="AL130" s="42"/>
+      <c r="AM130" s="42"/>
+      <c r="AN130" s="42"/>
+      <c r="AO130" s="43"/>
     </row>
     <row r="131" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
@@ -10182,10 +10182,10 @@
       <c r="AO180" s="12"/>
     </row>
     <row r="182" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A182" s="42" t="s">
+      <c r="A182" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="B182" s="42"/>
+      <c r="B182" s="44"/>
     </row>
     <row r="183" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A183" s="13" t="s">

--- a/Rekap Barang September.xlsx
+++ b/Rekap Barang September.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF47BCFB-A32B-4D64-A477-3D01CF1FA8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F4FC35-2E02-426D-B37B-776CF75C2524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7425" yWindow="0" windowWidth="13170" windowHeight="10905" xr2:uid="{F7CA82D4-8FEC-46C5-8E3D-E43D8F29F763}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F7CA82D4-8FEC-46C5-8E3D-E43D8F29F763}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="176">
   <si>
     <t>No</t>
   </si>
@@ -562,6 +562,9 @@
   </si>
   <si>
     <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>Colokan</t>
   </si>
 </sst>
 </file>
@@ -829,15 +832,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -848,6 +842,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1184,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551225FE-23E4-42F3-B08F-0D37368591A6}">
-  <dimension ref="A1:AO211"/>
+  <dimension ref="A1:AO212"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="9" customWidth="1"/>
@@ -1197,50 +1200,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="41"/>
-      <c r="AG1" s="41"/>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
       <c r="AJ1" s="8"/>
     </row>
     <row r="2" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="38"/>
+      <c r="B2" s="35"/>
     </row>
     <row r="3" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -1349,13 +1352,13 @@
         <v>3</v>
       </c>
       <c r="AJ3" s="10"/>
-      <c r="AK3" s="35" t="s">
+      <c r="AK3" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AL3" s="36"/>
-      <c r="AM3" s="36"/>
-      <c r="AN3" s="36"/>
-      <c r="AO3" s="37"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="40"/>
+      <c r="AO3" s="41"/>
     </row>
     <row r="4" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
@@ -1384,7 +1387,9 @@
       <c r="N4" s="7">
         <v>2</v>
       </c>
-      <c r="O4" s="7"/>
+      <c r="O4" s="7">
+        <v>1</v>
+      </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -1405,8 +1410,8 @@
       <c r="AG4" s="7"/>
       <c r="AH4" s="7"/>
       <c r="AI4" s="6">
-        <f>C4-D4-E4-F4-G4-H4-I4-J4-K4-L4-M4-N4-O4-P4-Q4-R4-S4-T4-U4-V4-W4-X4-Y4-Z4-AA4-AB4-AC4-AD4-AE4-AF4-AG4-AH4</f>
-        <v>24</v>
+        <f>C4-D4-E4-F4-G4-H4-I4-J4-K4-L4-M4-N4-O4</f>
+        <v>23</v>
       </c>
       <c r="AJ4" s="10"/>
       <c r="AK4" s="2"/>
@@ -2254,7 +2259,9 @@
       <c r="AO20" s="2"/>
     </row>
     <row r="21" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
+      <c r="A21" s="6">
+        <v>18</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>159</v>
       </c>
@@ -2274,7 +2281,9 @@
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
+      <c r="O21" s="7">
+        <v>1</v>
+      </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
@@ -2296,7 +2305,7 @@
       <c r="AH21" s="7"/>
       <c r="AI21" s="6">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ21" s="10"/>
       <c r="AK21" s="32">
@@ -2309,7 +2318,7 @@
     </row>
     <row r="22" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>50</v>
@@ -2361,7 +2370,7 @@
     </row>
     <row r="23" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>51</v>
@@ -2382,7 +2391,9 @@
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
+      <c r="O23" s="7">
+        <v>2</v>
+      </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
@@ -2404,7 +2415,7 @@
       <c r="AH23" s="7"/>
       <c r="AI23" s="6">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ23" s="10"/>
       <c r="AK23" s="32">
@@ -2417,7 +2428,7 @@
     </row>
     <row r="24" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>52</v>
@@ -2436,7 +2447,9 @@
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
+      <c r="O24" s="7">
+        <v>2</v>
+      </c>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
@@ -2458,7 +2471,7 @@
       <c r="AH24" s="7"/>
       <c r="AI24" s="6">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ24" s="10"/>
       <c r="AK24" s="2"/>
@@ -2469,7 +2482,7 @@
     </row>
     <row r="25" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>53</v>
@@ -2525,7 +2538,7 @@
     </row>
     <row r="26" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>54</v>
@@ -2577,7 +2590,7 @@
     </row>
     <row r="27" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>55</v>
@@ -2629,7 +2642,7 @@
     </row>
     <row r="28" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>56</v>
@@ -2694,12 +2707,12 @@
       <c r="A32" s="10"/>
     </row>
     <row r="33" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="38"/>
-    </row>
-    <row r="34" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+      <c r="B33" s="35"/>
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>0</v>
       </c>
@@ -2806,15 +2819,15 @@
         <v>3</v>
       </c>
       <c r="AJ34" s="10"/>
-      <c r="AK34" s="35" t="s">
+      <c r="AK34" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AL34" s="36"/>
-      <c r="AM34" s="36"/>
-      <c r="AN34" s="36"/>
-      <c r="AO34" s="37"/>
-    </row>
-    <row r="35" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+      <c r="AL34" s="40"/>
+      <c r="AM34" s="40"/>
+      <c r="AN34" s="40"/>
+      <c r="AO34" s="41"/>
+    </row>
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>1</v>
       </c>
@@ -2870,7 +2883,7 @@
       <c r="AN35" s="2"/>
       <c r="AO35" s="2"/>
     </row>
-    <row r="36" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>2</v>
       </c>
@@ -2922,7 +2935,7 @@
       <c r="AN36" s="2"/>
       <c r="AO36" s="2"/>
     </row>
-    <row r="37" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>3</v>
       </c>
@@ -2974,7 +2987,7 @@
       <c r="AN37" s="2"/>
       <c r="AO37" s="2"/>
     </row>
-    <row r="38" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>4</v>
       </c>
@@ -3026,7 +3039,7 @@
       <c r="AN38" s="2"/>
       <c r="AO38" s="2"/>
     </row>
-    <row r="39" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>5</v>
       </c>
@@ -3078,7 +3091,7 @@
       <c r="AN39" s="2"/>
       <c r="AO39" s="2"/>
     </row>
-    <row r="40" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>6</v>
       </c>
@@ -3130,7 +3143,7 @@
       <c r="AN40" s="2"/>
       <c r="AO40" s="2"/>
     </row>
-    <row r="41" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="2" t="s">
         <v>171</v>
@@ -3182,7 +3195,7 @@
       <c r="AN41" s="2"/>
       <c r="AO41" s="2"/>
     </row>
-    <row r="42" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>7</v>
       </c>
@@ -3234,7 +3247,7 @@
       <c r="AN42" s="2"/>
       <c r="AO42" s="2"/>
     </row>
-    <row r="43" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>8</v>
       </c>
@@ -3286,7 +3299,7 @@
       <c r="AN43" s="2"/>
       <c r="AO43" s="2"/>
     </row>
-    <row r="44" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>9</v>
       </c>
@@ -3338,7 +3351,7 @@
       <c r="AN44" s="2"/>
       <c r="AO44" s="2"/>
     </row>
-    <row r="45" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>10</v>
       </c>
@@ -3390,7 +3403,7 @@
       <c r="AN45" s="2"/>
       <c r="AO45" s="2"/>
     </row>
-    <row r="46" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>11</v>
       </c>
@@ -3442,7 +3455,7 @@
       <c r="AN46" s="2"/>
       <c r="AO46" s="2"/>
     </row>
-    <row r="47" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>12</v>
       </c>
@@ -3494,23 +3507,23 @@
       <c r="AN47" s="2"/>
       <c r="AO47" s="2"/>
     </row>
-    <row r="48" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
     </row>
-    <row r="49" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
     </row>
-    <row r="50" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50" s="10"/>
     </row>
-    <row r="51" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
     </row>
-    <row r="52" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
-      <c r="A52" s="39" t="s">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A52" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="B52" s="39"/>
+      <c r="B52" s="36"/>
       <c r="C52" s="15"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
@@ -3546,7 +3559,7 @@
       <c r="AI52" s="17"/>
       <c r="AJ52" s="17"/>
     </row>
-    <row r="53" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>0</v>
       </c>
@@ -3653,15 +3666,15 @@
         <v>3</v>
       </c>
       <c r="AJ53" s="15"/>
-      <c r="AK53" s="35" t="s">
+      <c r="AK53" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AL53" s="36"/>
-      <c r="AM53" s="36"/>
-      <c r="AN53" s="36"/>
-      <c r="AO53" s="37"/>
-    </row>
-    <row r="54" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+      <c r="AL53" s="40"/>
+      <c r="AM53" s="40"/>
+      <c r="AN53" s="40"/>
+      <c r="AO53" s="41"/>
+    </row>
+    <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" s="23">
         <v>1</v>
       </c>
@@ -3719,7 +3732,7 @@
       <c r="AN54" s="2"/>
       <c r="AO54" s="2"/>
     </row>
-    <row r="55" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" s="23">
         <v>2</v>
       </c>
@@ -3771,7 +3784,7 @@
       <c r="AN55" s="2"/>
       <c r="AO55" s="2"/>
     </row>
-    <row r="56" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" s="23">
         <v>3</v>
       </c>
@@ -3823,7 +3836,7 @@
       <c r="AN56" s="2"/>
       <c r="AO56" s="2"/>
     </row>
-    <row r="57" spans="1:41" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" s="23">
         <v>4</v>
       </c>
@@ -4026,7 +4039,9 @@
       <c r="N60" s="25">
         <v>1</v>
       </c>
-      <c r="O60" s="25"/>
+      <c r="O60" s="25">
+        <v>2</v>
+      </c>
       <c r="P60" s="25"/>
       <c r="Q60" s="25"/>
       <c r="R60" s="25"/>
@@ -4048,7 +4063,7 @@
       <c r="AH60" s="25"/>
       <c r="AI60" s="5">
         <f t="shared" si="2"/>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ60" s="15"/>
       <c r="AK60" s="2"/>
@@ -4250,7 +4265,9 @@
       <c r="N64" s="25">
         <v>21</v>
       </c>
-      <c r="O64" s="25"/>
+      <c r="O64" s="25">
+        <v>85</v>
+      </c>
       <c r="P64" s="25"/>
       <c r="Q64" s="25"/>
       <c r="R64" s="25"/>
@@ -4270,9 +4287,9 @@
       <c r="AF64" s="25"/>
       <c r="AG64" s="25"/>
       <c r="AH64" s="25"/>
-      <c r="AI64" s="5" t="e">
-        <f>C64-D64-E64-#REF!-F64-H64-I64-J64-K64-L64-M64-N64-O64-P64-Q64-R64-S64-T64-U64-V64-W64-X64-Y64-Z64-AA64-AB64-AC64-AD64-AE64-AF64-AG64-AH64</f>
-        <v>#REF!</v>
+      <c r="AI64" s="5">
+        <f>C64-D64-E64--F64-H64-I64-J64-K64-L64-M64-N64-O64-P64-Q64-R64-S64-T64-U64-V64-W64-X64-Y64-Z64-AA64-AB64-AC64-AD64-AE64-AF64-AG64-AH64</f>
+        <v>1731</v>
       </c>
       <c r="AJ64" s="15"/>
       <c r="AK64" s="2"/>
@@ -4324,7 +4341,10 @@
       <c r="AF65" s="25"/>
       <c r="AG65" s="25"/>
       <c r="AH65" s="25"/>
-      <c r="AI65" s="5"/>
+      <c r="AI65" s="5">
+        <f t="shared" ref="AI65:AI74" si="3">C65-D65-E65--F65-H65-I65-J65-K65-L65-M65-N65-O65-P65-Q65-R65-S65-T65-U65-V65-W65-X65-Y65-Z65-AA65-AB65-AC65-AD65-AE65-AF65-AG65-AH65</f>
+        <v>173</v>
+      </c>
       <c r="AJ65" s="15"/>
       <c r="AK65" s="2"/>
       <c r="AL65" s="2"/>
@@ -4355,7 +4375,9 @@
       <c r="L66" s="25"/>
       <c r="M66" s="25"/>
       <c r="N66" s="25"/>
-      <c r="O66" s="25"/>
+      <c r="O66" s="25">
+        <v>189</v>
+      </c>
       <c r="P66" s="25"/>
       <c r="Q66" s="25"/>
       <c r="R66" s="25"/>
@@ -4376,8 +4398,8 @@
       <c r="AG66" s="25"/>
       <c r="AH66" s="25"/>
       <c r="AI66" s="5">
-        <f t="shared" si="2"/>
-        <v>555</v>
+        <f t="shared" si="3"/>
+        <v>366</v>
       </c>
       <c r="AJ66" s="15"/>
       <c r="AK66" s="2"/>
@@ -4434,7 +4456,7 @@
       <c r="AG67" s="25"/>
       <c r="AH67" s="25"/>
       <c r="AI67" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>464</v>
       </c>
       <c r="AJ67" s="15"/>
@@ -4469,7 +4491,9 @@
         <v>4</v>
       </c>
       <c r="N68" s="25"/>
-      <c r="O68" s="25"/>
+      <c r="O68" s="25">
+        <v>4</v>
+      </c>
       <c r="P68" s="25"/>
       <c r="Q68" s="25"/>
       <c r="R68" s="25"/>
@@ -4489,7 +4513,10 @@
       <c r="AF68" s="25"/>
       <c r="AG68" s="25"/>
       <c r="AH68" s="25"/>
-      <c r="AI68" s="5"/>
+      <c r="AI68" s="5">
+        <f t="shared" si="3"/>
+        <v>282</v>
+      </c>
       <c r="AJ68" s="15"/>
       <c r="AK68" s="2"/>
       <c r="AL68" s="2"/>
@@ -4522,7 +4549,9 @@
       <c r="L69" s="25"/>
       <c r="M69" s="25"/>
       <c r="N69" s="25"/>
-      <c r="O69" s="25"/>
+      <c r="O69" s="25">
+        <v>37</v>
+      </c>
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25"/>
@@ -4543,8 +4572,8 @@
       <c r="AG69" s="25"/>
       <c r="AH69" s="25"/>
       <c r="AI69" s="5">
-        <f t="shared" si="2"/>
-        <v>154</v>
+        <f t="shared" si="3"/>
+        <v>117</v>
       </c>
       <c r="AJ69" s="15"/>
       <c r="AK69" s="2"/>
@@ -4596,7 +4625,10 @@
       <c r="AF70" s="25"/>
       <c r="AG70" s="25"/>
       <c r="AH70" s="25"/>
-      <c r="AI70" s="5"/>
+      <c r="AI70" s="5">
+        <f t="shared" si="3"/>
+        <v>-5</v>
+      </c>
       <c r="AJ70" s="15"/>
       <c r="AK70" s="2"/>
       <c r="AL70" s="2"/>
@@ -4645,7 +4677,10 @@
       <c r="AF71" s="25"/>
       <c r="AG71" s="25"/>
       <c r="AH71" s="25"/>
-      <c r="AI71" s="5"/>
+      <c r="AI71" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AJ71" s="15"/>
       <c r="AK71" s="2"/>
       <c r="AL71" s="2"/>
@@ -4694,7 +4729,10 @@
       <c r="AF72" s="25"/>
       <c r="AG72" s="25"/>
       <c r="AH72" s="25"/>
-      <c r="AI72" s="5"/>
+      <c r="AI72" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AJ72" s="15"/>
       <c r="AK72" s="2"/>
       <c r="AL72" s="2"/>
@@ -4743,7 +4781,10 @@
       <c r="AF73" s="25"/>
       <c r="AG73" s="25"/>
       <c r="AH73" s="25"/>
-      <c r="AI73" s="5"/>
+      <c r="AI73" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AJ73" s="15"/>
       <c r="AK73" s="2"/>
       <c r="AL73" s="2"/>
@@ -4792,7 +4833,10 @@
       <c r="AF74" s="25"/>
       <c r="AG74" s="25"/>
       <c r="AH74" s="25"/>
-      <c r="AI74" s="5"/>
+      <c r="AI74" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="AJ74" s="15"/>
       <c r="AK74" s="2"/>
       <c r="AL74" s="2"/>
@@ -5305,7 +5349,9 @@
       <c r="L84" s="26"/>
       <c r="M84" s="26"/>
       <c r="N84" s="26"/>
-      <c r="O84" s="26"/>
+      <c r="O84" s="26">
+        <v>1</v>
+      </c>
       <c r="P84" s="26"/>
       <c r="Q84" s="26"/>
       <c r="R84" s="26"/>
@@ -5327,7 +5373,7 @@
       <c r="AH84" s="26"/>
       <c r="AI84" s="5">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ84" s="15"/>
       <c r="AK84" s="2"/>
@@ -5959,7 +6005,9 @@
       </c>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
+      <c r="O97" s="7">
+        <v>4</v>
+      </c>
       <c r="P97" s="7"/>
       <c r="Q97" s="7"/>
       <c r="R97" s="7"/>
@@ -5981,12 +6029,51 @@
       <c r="AH97" s="7"/>
       <c r="AI97" s="5">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
-      <c r="AI98" s="15"/>
+      <c r="A98" s="5">
+        <v>43</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="6"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
+      <c r="M98" s="7"/>
+      <c r="N98" s="7"/>
+      <c r="O98" s="7">
+        <v>1</v>
+      </c>
+      <c r="P98" s="7"/>
+      <c r="Q98" s="7"/>
+      <c r="R98" s="7"/>
+      <c r="S98" s="7"/>
+      <c r="T98" s="7"/>
+      <c r="U98" s="7"/>
+      <c r="V98" s="7"/>
+      <c r="W98" s="7"/>
+      <c r="X98" s="7"/>
+      <c r="Y98" s="7"/>
+      <c r="Z98" s="7"/>
+      <c r="AA98" s="7"/>
+      <c r="AB98" s="7"/>
+      <c r="AC98" s="7"/>
+      <c r="AD98" s="7"/>
+      <c r="AE98" s="7"/>
+      <c r="AF98" s="7"/>
+      <c r="AG98" s="7"/>
+      <c r="AH98" s="7"/>
+      <c r="AI98" s="5"/>
     </row>
     <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
@@ -5996,254 +6083,207 @@
       <c r="A100" s="15"/>
       <c r="AI100" s="15"/>
     </row>
-    <row r="103" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A103" s="39" t="s">
+    <row r="101" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A101" s="15"/>
+      <c r="AI101" s="15"/>
+    </row>
+    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A104" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="B103" s="39"/>
-      <c r="C103" s="17"/>
-      <c r="D103" s="16"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="16"/>
-      <c r="H103" s="16"/>
-      <c r="I103" s="16"/>
-      <c r="J103" s="16"/>
-      <c r="K103" s="16"/>
-      <c r="L103" s="16"/>
-      <c r="M103" s="16"/>
-      <c r="N103" s="16"/>
-      <c r="O103" s="16"/>
-      <c r="P103" s="16"/>
-      <c r="Q103" s="16"/>
-      <c r="R103" s="16"/>
-      <c r="S103" s="16"/>
-      <c r="T103" s="16"/>
-      <c r="U103" s="16"/>
-      <c r="V103" s="16"/>
-      <c r="W103" s="16"/>
-      <c r="X103" s="16"/>
-      <c r="Y103" s="16"/>
-      <c r="Z103" s="16"/>
-      <c r="AA103" s="16"/>
-      <c r="AB103" s="16"/>
-      <c r="AC103" s="16"/>
-      <c r="AD103" s="16"/>
-      <c r="AE103" s="16"/>
-      <c r="AF103" s="16"/>
-      <c r="AG103" s="16"/>
-      <c r="AH103" s="16"/>
-      <c r="AI103" s="17"/>
-    </row>
-    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A104" s="18" t="s">
+      <c r="B104" s="36"/>
+      <c r="C104" s="17"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="16"/>
+      <c r="J104" s="16"/>
+      <c r="K104" s="16"/>
+      <c r="L104" s="16"/>
+      <c r="M104" s="16"/>
+      <c r="N104" s="16"/>
+      <c r="O104" s="16"/>
+      <c r="P104" s="16"/>
+      <c r="Q104" s="16"/>
+      <c r="R104" s="16"/>
+      <c r="S104" s="16"/>
+      <c r="T104" s="16"/>
+      <c r="U104" s="16"/>
+      <c r="V104" s="16"/>
+      <c r="W104" s="16"/>
+      <c r="X104" s="16"/>
+      <c r="Y104" s="16"/>
+      <c r="Z104" s="16"/>
+      <c r="AA104" s="16"/>
+      <c r="AB104" s="16"/>
+      <c r="AC104" s="16"/>
+      <c r="AD104" s="16"/>
+      <c r="AE104" s="16"/>
+      <c r="AF104" s="16"/>
+      <c r="AG104" s="16"/>
+      <c r="AH104" s="16"/>
+      <c r="AI104" s="17"/>
+    </row>
+    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A105" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B104" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C104" s="27" t="s">
+      <c r="B105" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D104" s="21">
-        <v>1</v>
-      </c>
-      <c r="E104" s="21">
+      <c r="D105" s="21">
+        <v>1</v>
+      </c>
+      <c r="E105" s="21">
         <v>2</v>
       </c>
-      <c r="F104" s="21">
+      <c r="F105" s="21">
         <v>3</v>
       </c>
-      <c r="G104" s="21">
+      <c r="G105" s="21">
         <v>4</v>
       </c>
-      <c r="H104" s="21">
+      <c r="H105" s="21">
         <v>5</v>
       </c>
-      <c r="I104" s="21">
+      <c r="I105" s="21">
         <v>6</v>
       </c>
-      <c r="J104" s="21">
+      <c r="J105" s="21">
         <v>7</v>
       </c>
-      <c r="K104" s="21">
+      <c r="K105" s="21">
         <v>8</v>
       </c>
-      <c r="L104" s="21">
+      <c r="L105" s="21">
         <v>9</v>
       </c>
-      <c r="M104" s="21">
+      <c r="M105" s="21">
         <v>10</v>
       </c>
-      <c r="N104" s="21">
+      <c r="N105" s="21">
         <v>11</v>
       </c>
-      <c r="O104" s="21">
+      <c r="O105" s="21">
         <v>12</v>
       </c>
-      <c r="P104" s="21">
+      <c r="P105" s="21">
         <v>13</v>
       </c>
-      <c r="Q104" s="21">
+      <c r="Q105" s="21">
         <v>14</v>
       </c>
-      <c r="R104" s="21">
+      <c r="R105" s="21">
         <v>15</v>
       </c>
-      <c r="S104" s="21">
+      <c r="S105" s="21">
         <v>16</v>
       </c>
-      <c r="T104" s="21">
+      <c r="T105" s="21">
         <v>17</v>
       </c>
-      <c r="U104" s="21">
+      <c r="U105" s="21">
         <v>18</v>
       </c>
-      <c r="V104" s="21">
+      <c r="V105" s="21">
         <v>19</v>
       </c>
-      <c r="W104" s="21">
+      <c r="W105" s="21">
         <v>20</v>
       </c>
-      <c r="X104" s="21">
+      <c r="X105" s="21">
         <v>21</v>
       </c>
-      <c r="Y104" s="21">
+      <c r="Y105" s="21">
         <v>22</v>
       </c>
-      <c r="Z104" s="21">
+      <c r="Z105" s="21">
         <v>23</v>
       </c>
-      <c r="AA104" s="21">
+      <c r="AA105" s="21">
         <v>24</v>
       </c>
-      <c r="AB104" s="21">
+      <c r="AB105" s="21">
         <v>25</v>
       </c>
-      <c r="AC104" s="21">
+      <c r="AC105" s="21">
         <v>26</v>
       </c>
-      <c r="AD104" s="21">
+      <c r="AD105" s="21">
         <v>27</v>
       </c>
-      <c r="AE104" s="21">
+      <c r="AE105" s="21">
         <v>28</v>
       </c>
-      <c r="AF104" s="21">
+      <c r="AF105" s="21">
         <v>29</v>
       </c>
-      <c r="AG104" s="21">
+      <c r="AG105" s="21">
         <v>30</v>
       </c>
-      <c r="AH104" s="21">
+      <c r="AH105" s="21">
         <v>31</v>
       </c>
-      <c r="AI104" s="20" t="s">
+      <c r="AI105" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="AK104" s="35" t="s">
+      <c r="AK105" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AL104" s="36"/>
-      <c r="AM104" s="36"/>
-      <c r="AN104" s="36"/>
-      <c r="AO104" s="37"/>
-    </row>
-    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
-        <v>1</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C105" s="5">
-        <v>3</v>
-      </c>
-      <c r="D105" s="26"/>
-      <c r="E105" s="26"/>
-      <c r="F105" s="26"/>
-      <c r="G105" s="26"/>
-      <c r="H105" s="26"/>
-      <c r="I105" s="26"/>
-      <c r="J105" s="26"/>
-      <c r="K105" s="26"/>
-      <c r="L105" s="26"/>
-      <c r="M105" s="26"/>
-      <c r="N105" s="26"/>
-      <c r="O105" s="26"/>
-      <c r="P105" s="26"/>
-      <c r="Q105" s="26"/>
-      <c r="R105" s="26"/>
-      <c r="S105" s="26"/>
-      <c r="T105" s="26"/>
-      <c r="U105" s="26"/>
-      <c r="V105" s="26"/>
-      <c r="W105" s="26"/>
-      <c r="X105" s="26"/>
-      <c r="Y105" s="26"/>
-      <c r="Z105" s="26"/>
-      <c r="AA105" s="26"/>
-      <c r="AB105" s="26"/>
-      <c r="AC105" s="26"/>
-      <c r="AD105" s="26"/>
-      <c r="AE105" s="26"/>
-      <c r="AF105" s="26"/>
-      <c r="AG105" s="26"/>
-      <c r="AH105" s="26"/>
-      <c r="AI105" s="5">
-        <f>C105-E105-F105-G105-H105-I105-J105-K105-M105-N105-O105-P105-Q105-R105-S105-T105-U105-V105-W105-X105-Y105-Z105-AA105-AB105-AC105-AD105-AE105-AF105-AG105-AH105</f>
-        <v>3</v>
-      </c>
-      <c r="AK105" s="2"/>
-      <c r="AL105" s="2"/>
-      <c r="AM105" s="2"/>
-      <c r="AN105" s="2"/>
-      <c r="AO105" s="2"/>
+      <c r="AL105" s="40"/>
+      <c r="AM105" s="40"/>
+      <c r="AN105" s="40"/>
+      <c r="AO105" s="41"/>
     </row>
     <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
-        <v>2</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="C106" s="5">
-        <v>1</v>
-      </c>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-      <c r="H106" s="7"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="7"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7"/>
-      <c r="N106" s="7"/>
-      <c r="O106" s="7"/>
-      <c r="P106" s="7"/>
-      <c r="Q106" s="7"/>
-      <c r="R106" s="7"/>
-      <c r="S106" s="7"/>
-      <c r="T106" s="7"/>
-      <c r="U106" s="7"/>
-      <c r="V106" s="7"/>
-      <c r="W106" s="7"/>
-      <c r="X106" s="7"/>
-      <c r="Y106" s="7"/>
-      <c r="Z106" s="7"/>
-      <c r="AA106" s="7"/>
-      <c r="AB106" s="7"/>
-      <c r="AC106" s="7"/>
-      <c r="AD106" s="7"/>
-      <c r="AE106" s="7"/>
-      <c r="AF106" s="7"/>
-      <c r="AG106" s="7"/>
-      <c r="AH106" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="26"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="26"/>
+      <c r="H106" s="26"/>
+      <c r="I106" s="26"/>
+      <c r="J106" s="26"/>
+      <c r="K106" s="26"/>
+      <c r="L106" s="26"/>
+      <c r="M106" s="26"/>
+      <c r="N106" s="26"/>
+      <c r="O106" s="26"/>
+      <c r="P106" s="26"/>
+      <c r="Q106" s="26"/>
+      <c r="R106" s="26"/>
+      <c r="S106" s="26"/>
+      <c r="T106" s="26"/>
+      <c r="U106" s="26"/>
+      <c r="V106" s="26"/>
+      <c r="W106" s="26"/>
+      <c r="X106" s="26"/>
+      <c r="Y106" s="26"/>
+      <c r="Z106" s="26"/>
+      <c r="AA106" s="26"/>
+      <c r="AB106" s="26"/>
+      <c r="AC106" s="26"/>
+      <c r="AD106" s="26"/>
+      <c r="AE106" s="26"/>
+      <c r="AF106" s="26"/>
+      <c r="AG106" s="26"/>
+      <c r="AH106" s="26"/>
       <c r="AI106" s="5">
-        <f t="shared" ref="AI106:AI137" si="3">C106-E106-F106-G106-H106-I106-J106-K106-M106-N106-O106-P106-Q106-R106-S106-T106-U106-V106-W106-X106-Y106-Z106-AA106-AB106-AC106-AD106-AE106-AF106-AG106-AH106</f>
-        <v>1</v>
+        <f>C106-E106-F106-G106-H106-I106-J106-K106-M106-N106-O106-P106-Q106-R106-S106-T106-U106-V106-W106-X106-Y106-Z106-AA106-AB106-AC106-AD106-AE106-AF106-AG106-AH106</f>
+        <v>3</v>
       </c>
       <c r="AK106" s="2"/>
       <c r="AL106" s="2"/>
@@ -6253,13 +6293,13 @@
     </row>
     <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C107" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -6293,8 +6333,8 @@
       <c r="AG107" s="7"/>
       <c r="AH107" s="7"/>
       <c r="AI107" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" ref="AI107:AI138" si="4">C107-E107-F107-G107-H107-I107-J107-K107-M107-N107-O107-P107-Q107-R107-S107-T107-U107-V107-W107-X107-Y107-Z107-AA107-AB107-AC107-AD107-AE107-AF107-AG107-AH107</f>
+        <v>1</v>
       </c>
       <c r="AK107" s="2"/>
       <c r="AL107" s="2"/>
@@ -6304,13 +6344,13 @@
     </row>
     <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C108" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
@@ -6344,8 +6384,8 @@
       <c r="AG108" s="7"/>
       <c r="AH108" s="7"/>
       <c r="AI108" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AK108" s="2"/>
       <c r="AL108" s="2"/>
@@ -6355,10 +6395,10 @@
     </row>
     <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C109" s="5">
         <v>1</v>
@@ -6395,7 +6435,7 @@
       <c r="AG109" s="7"/>
       <c r="AH109" s="7"/>
       <c r="AI109" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK109" s="2"/>
@@ -6406,10 +6446,10 @@
     </row>
     <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C110" s="5">
         <v>1</v>
@@ -6446,7 +6486,7 @@
       <c r="AG110" s="7"/>
       <c r="AH110" s="7"/>
       <c r="AI110" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK110" s="2"/>
@@ -6457,13 +6497,13 @@
     </row>
     <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C111" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
@@ -6497,8 +6537,8 @@
       <c r="AG111" s="7"/>
       <c r="AH111" s="7"/>
       <c r="AI111" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="AK111" s="2"/>
       <c r="AL111" s="2"/>
@@ -6508,13 +6548,13 @@
     </row>
     <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C112" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
@@ -6548,8 +6588,8 @@
       <c r="AG112" s="7"/>
       <c r="AH112" s="7"/>
       <c r="AI112" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AK112" s="2"/>
       <c r="AL112" s="2"/>
@@ -6559,12 +6599,12 @@
     </row>
     <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C113" s="6">
+        <v>66</v>
+      </c>
+      <c r="C113" s="5">
         <v>1</v>
       </c>
       <c r="D113" s="7"/>
@@ -6599,7 +6639,7 @@
       <c r="AG113" s="7"/>
       <c r="AH113" s="7"/>
       <c r="AI113" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK113" s="2"/>
@@ -6610,10 +6650,10 @@
     </row>
     <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C114" s="6">
         <v>1</v>
@@ -6650,7 +6690,7 @@
       <c r="AG114" s="7"/>
       <c r="AH114" s="7"/>
       <c r="AI114" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK114" s="2"/>
@@ -6661,10 +6701,10 @@
     </row>
     <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C115" s="6">
         <v>1</v>
@@ -6701,7 +6741,7 @@
       <c r="AG115" s="7"/>
       <c r="AH115" s="7"/>
       <c r="AI115" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK115" s="2"/>
@@ -6712,13 +6752,13 @@
     </row>
     <row r="116" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C116" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
@@ -6752,8 +6792,8 @@
       <c r="AG116" s="7"/>
       <c r="AH116" s="7"/>
       <c r="AI116" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="AK116" s="2"/>
       <c r="AL116" s="2"/>
@@ -6763,13 +6803,13 @@
     </row>
     <row r="117" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C117" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
@@ -6803,8 +6843,8 @@
       <c r="AG117" s="7"/>
       <c r="AH117" s="7"/>
       <c r="AI117" s="5">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AK117" s="2"/>
       <c r="AL117" s="2"/>
@@ -6814,13 +6854,13 @@
     </row>
     <row r="118" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C118" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
@@ -6854,8 +6894,8 @@
       <c r="AG118" s="7"/>
       <c r="AH118" s="7"/>
       <c r="AI118" s="5">
-        <f t="shared" si="3"/>
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="AK118" s="2"/>
       <c r="AL118" s="2"/>
@@ -6865,13 +6905,13 @@
     </row>
     <row r="119" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C119" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
@@ -6905,8 +6945,8 @@
       <c r="AG119" s="7"/>
       <c r="AH119" s="7"/>
       <c r="AI119" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="AK119" s="2"/>
       <c r="AL119" s="2"/>
@@ -6916,13 +6956,13 @@
     </row>
     <row r="120" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C120" s="6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -6956,8 +6996,8 @@
       <c r="AG120" s="7"/>
       <c r="AH120" s="7"/>
       <c r="AI120" s="5">
-        <f t="shared" si="3"/>
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="AK120" s="2"/>
       <c r="AL120" s="2"/>
@@ -6967,13 +7007,13 @@
     </row>
     <row r="121" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C121" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
@@ -7007,8 +7047,8 @@
       <c r="AG121" s="7"/>
       <c r="AH121" s="7"/>
       <c r="AI121" s="5">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="AK121" s="2"/>
       <c r="AL121" s="2"/>
@@ -7018,13 +7058,13 @@
     </row>
     <row r="122" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C122" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
@@ -7058,8 +7098,8 @@
       <c r="AG122" s="7"/>
       <c r="AH122" s="7"/>
       <c r="AI122" s="5">
-        <f t="shared" si="3"/>
-        <v>9</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="AK122" s="2"/>
       <c r="AL122" s="2"/>
@@ -7069,13 +7109,13 @@
     </row>
     <row r="123" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C123" s="6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -7109,8 +7149,8 @@
       <c r="AG123" s="7"/>
       <c r="AH123" s="7"/>
       <c r="AI123" s="5">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>9</v>
       </c>
       <c r="AK123" s="2"/>
       <c r="AL123" s="2"/>
@@ -7120,13 +7160,13 @@
     </row>
     <row r="124" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C124" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -7160,8 +7200,8 @@
       <c r="AG124" s="7"/>
       <c r="AH124" s="7"/>
       <c r="AI124" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="AK124" s="2"/>
       <c r="AL124" s="2"/>
@@ -7171,13 +7211,13 @@
     </row>
     <row r="125" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C125" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -7211,8 +7251,8 @@
       <c r="AG125" s="7"/>
       <c r="AH125" s="7"/>
       <c r="AI125" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="AK125" s="2"/>
       <c r="AL125" s="2"/>
@@ -7222,13 +7262,13 @@
     </row>
     <row r="126" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -7262,8 +7302,8 @@
       <c r="AG126" s="7"/>
       <c r="AH126" s="7"/>
       <c r="AI126" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="AK126" s="2"/>
       <c r="AL126" s="2"/>
@@ -7273,13 +7313,13 @@
     </row>
     <row r="127" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C127" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -7313,8 +7353,8 @@
       <c r="AG127" s="7"/>
       <c r="AH127" s="7"/>
       <c r="AI127" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AK127" s="2"/>
       <c r="AL127" s="2"/>
@@ -7324,25 +7364,21 @@
     </row>
     <row r="128" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C128" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
-      <c r="G128" s="7">
-        <v>1</v>
-      </c>
+      <c r="G128" s="7"/>
       <c r="H128" s="7"/>
       <c r="I128" s="7"/>
-      <c r="J128" s="7">
-        <v>1</v>
-      </c>
+      <c r="J128" s="7"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c r="M128" s="7"/>
@@ -7368,8 +7404,8 @@
       <c r="AG128" s="7"/>
       <c r="AH128" s="7"/>
       <c r="AI128" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="AK128" s="2"/>
       <c r="AL128" s="2"/>
@@ -7379,21 +7415,25 @@
     </row>
     <row r="129" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C129" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
+      <c r="G129" s="7">
+        <v>1</v>
+      </c>
       <c r="H129" s="7"/>
       <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
+      <c r="J129" s="7">
+        <v>1</v>
+      </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
@@ -7419,8 +7459,8 @@
       <c r="AG129" s="7"/>
       <c r="AH129" s="7"/>
       <c r="AI129" s="5">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AK129" s="2"/>
       <c r="AL129" s="2"/>
@@ -7430,13 +7470,13 @@
     </row>
     <row r="130" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -7470,8 +7510,8 @@
       <c r="AG130" s="7"/>
       <c r="AH130" s="7"/>
       <c r="AI130" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="AK130" s="2"/>
       <c r="AL130" s="2"/>
@@ -7481,13 +7521,13 @@
     </row>
     <row r="131" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C131" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -7521,8 +7561,8 @@
       <c r="AG131" s="7"/>
       <c r="AH131" s="7"/>
       <c r="AI131" s="5">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="AK131" s="2"/>
       <c r="AL131" s="2"/>
@@ -7532,10 +7572,10 @@
     </row>
     <row r="132" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -7572,7 +7612,7 @@
       <c r="AG132" s="7"/>
       <c r="AH132" s="7"/>
       <c r="AI132" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK132" s="2"/>
@@ -7583,10 +7623,10 @@
     </row>
     <row r="133" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C133" s="6">
         <v>1</v>
@@ -7623,7 +7663,7 @@
       <c r="AG133" s="7"/>
       <c r="AH133" s="7"/>
       <c r="AI133" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AK133" s="2"/>
@@ -7634,13 +7674,13 @@
     </row>
     <row r="134" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C134" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -7674,8 +7714,8 @@
       <c r="AG134" s="7"/>
       <c r="AH134" s="7"/>
       <c r="AI134" s="5">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="4"/>
+        <v>1</v>
       </c>
       <c r="AK134" s="2"/>
       <c r="AL134" s="2"/>
@@ -7685,20 +7725,18 @@
     </row>
     <row r="135" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C135" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
-      <c r="G135" s="7">
-        <v>1</v>
-      </c>
+      <c r="G135" s="7"/>
       <c r="H135" s="7"/>
       <c r="I135" s="7"/>
       <c r="J135" s="7"/>
@@ -7727,7 +7765,7 @@
       <c r="AG135" s="7"/>
       <c r="AH135" s="7"/>
       <c r="AI135" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AK135" s="2"/>
@@ -7737,288 +7775,290 @@
       <c r="AO135" s="2"/>
     </row>
     <row r="136" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A136" s="28">
+      <c r="A136" s="5">
+        <v>31</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C136" s="6">
+        <v>3</v>
+      </c>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7">
+        <v>1</v>
+      </c>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="7"/>
+      <c r="K136" s="7"/>
+      <c r="L136" s="7"/>
+      <c r="M136" s="7"/>
+      <c r="N136" s="7"/>
+      <c r="O136" s="7"/>
+      <c r="P136" s="7"/>
+      <c r="Q136" s="7"/>
+      <c r="R136" s="7"/>
+      <c r="S136" s="7"/>
+      <c r="T136" s="7"/>
+      <c r="U136" s="7"/>
+      <c r="V136" s="7"/>
+      <c r="W136" s="7"/>
+      <c r="X136" s="7"/>
+      <c r="Y136" s="7"/>
+      <c r="Z136" s="7"/>
+      <c r="AA136" s="7"/>
+      <c r="AB136" s="7"/>
+      <c r="AC136" s="7"/>
+      <c r="AD136" s="7"/>
+      <c r="AE136" s="7"/>
+      <c r="AF136" s="7"/>
+      <c r="AG136" s="7"/>
+      <c r="AH136" s="7"/>
+      <c r="AI136" s="5">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AK136" s="2"/>
+      <c r="AL136" s="2"/>
+      <c r="AM136" s="2"/>
+      <c r="AN136" s="2"/>
+      <c r="AO136" s="2"/>
+    </row>
+    <row r="137" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A137" s="28">
         <v>32</v>
       </c>
-      <c r="B136" s="29" t="s">
+      <c r="B137" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="C136" s="30">
+      <c r="C137" s="30">
         <v>5</v>
       </c>
-      <c r="D136" s="31"/>
-      <c r="E136" s="31"/>
-      <c r="F136" s="31"/>
-      <c r="G136" s="31"/>
-      <c r="H136" s="31"/>
-      <c r="I136" s="31"/>
-      <c r="J136" s="31"/>
-      <c r="K136" s="31"/>
-      <c r="L136" s="31"/>
-      <c r="M136" s="31"/>
-      <c r="N136" s="31"/>
-      <c r="O136" s="31"/>
-      <c r="P136" s="31"/>
-      <c r="Q136" s="31"/>
-      <c r="R136" s="31"/>
-      <c r="S136" s="31"/>
-      <c r="T136" s="31"/>
-      <c r="U136" s="31"/>
-      <c r="V136" s="31"/>
-      <c r="W136" s="31"/>
-      <c r="X136" s="31"/>
-      <c r="Y136" s="31"/>
-      <c r="Z136" s="31"/>
-      <c r="AA136" s="31"/>
-      <c r="AB136" s="31"/>
-      <c r="AC136" s="31"/>
-      <c r="AD136" s="31"/>
-      <c r="AE136" s="31"/>
-      <c r="AF136" s="31"/>
-      <c r="AG136" s="31"/>
-      <c r="AH136" s="31"/>
-      <c r="AI136" s="28">
-        <f t="shared" si="3"/>
+      <c r="D137" s="31"/>
+      <c r="E137" s="31"/>
+      <c r="F137" s="31"/>
+      <c r="G137" s="31"/>
+      <c r="H137" s="31"/>
+      <c r="I137" s="31"/>
+      <c r="J137" s="31"/>
+      <c r="K137" s="31"/>
+      <c r="L137" s="31"/>
+      <c r="M137" s="31"/>
+      <c r="N137" s="31"/>
+      <c r="O137" s="31"/>
+      <c r="P137" s="31"/>
+      <c r="Q137" s="31"/>
+      <c r="R137" s="31"/>
+      <c r="S137" s="31"/>
+      <c r="T137" s="31"/>
+      <c r="U137" s="31"/>
+      <c r="V137" s="31"/>
+      <c r="W137" s="31"/>
+      <c r="X137" s="31"/>
+      <c r="Y137" s="31"/>
+      <c r="Z137" s="31"/>
+      <c r="AA137" s="31"/>
+      <c r="AB137" s="31"/>
+      <c r="AC137" s="31"/>
+      <c r="AD137" s="31"/>
+      <c r="AE137" s="31"/>
+      <c r="AF137" s="31"/>
+      <c r="AG137" s="31"/>
+      <c r="AH137" s="31"/>
+      <c r="AI137" s="28">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="AK136" s="29"/>
-      <c r="AL136" s="29"/>
-      <c r="AM136" s="29"/>
-      <c r="AN136" s="29"/>
-      <c r="AO136" s="29"/>
-    </row>
-    <row r="137" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A137" s="5">
+      <c r="AK137" s="29"/>
+      <c r="AL137" s="29"/>
+      <c r="AM137" s="29"/>
+      <c r="AN137" s="29"/>
+      <c r="AO137" s="29"/>
+    </row>
+    <row r="138" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A138" s="5">
         <v>33</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B138" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C138" s="6">
         <v>2</v>
       </c>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
-      <c r="K137" s="7"/>
-      <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="7"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="7"/>
-      <c r="T137" s="7"/>
-      <c r="U137" s="7"/>
-      <c r="V137" s="7"/>
-      <c r="W137" s="7"/>
-      <c r="X137" s="7"/>
-      <c r="Y137" s="7"/>
-      <c r="Z137" s="7"/>
-      <c r="AA137" s="7"/>
-      <c r="AB137" s="7"/>
-      <c r="AC137" s="7"/>
-      <c r="AD137" s="7"/>
-      <c r="AE137" s="7"/>
-      <c r="AF137" s="7"/>
-      <c r="AG137" s="7"/>
-      <c r="AH137" s="7"/>
-      <c r="AI137" s="5">
-        <f t="shared" si="3"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="7"/>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="M138" s="7"/>
+      <c r="N138" s="7"/>
+      <c r="O138" s="7"/>
+      <c r="P138" s="7"/>
+      <c r="Q138" s="7"/>
+      <c r="R138" s="7"/>
+      <c r="S138" s="7"/>
+      <c r="T138" s="7"/>
+      <c r="U138" s="7"/>
+      <c r="V138" s="7"/>
+      <c r="W138" s="7"/>
+      <c r="X138" s="7"/>
+      <c r="Y138" s="7"/>
+      <c r="Z138" s="7"/>
+      <c r="AA138" s="7"/>
+      <c r="AB138" s="7"/>
+      <c r="AC138" s="7"/>
+      <c r="AD138" s="7"/>
+      <c r="AE138" s="7"/>
+      <c r="AF138" s="7"/>
+      <c r="AG138" s="7"/>
+      <c r="AH138" s="7"/>
+      <c r="AI138" s="5">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AJ137" s="2"/>
-      <c r="AK137" s="2"/>
-      <c r="AL137" s="2"/>
-      <c r="AM137" s="2"/>
-      <c r="AN137" s="2"/>
-      <c r="AO137" s="2"/>
-    </row>
-    <row r="145" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A145" s="40" t="s">
+      <c r="AJ138" s="2"/>
+      <c r="AK138" s="2"/>
+      <c r="AL138" s="2"/>
+      <c r="AM138" s="2"/>
+      <c r="AN138" s="2"/>
+      <c r="AO138" s="2"/>
+    </row>
+    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A146" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="B145" s="40"/>
-    </row>
-    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A146" s="12" t="s">
+      <c r="B146" s="37"/>
+    </row>
+    <row r="147" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A147" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B146" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C146" s="13" t="s">
+      <c r="B147" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C147" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D146" s="13">
-        <v>1</v>
-      </c>
-      <c r="E146" s="13">
+      <c r="D147" s="13">
+        <v>1</v>
+      </c>
+      <c r="E147" s="13">
         <v>2</v>
       </c>
-      <c r="F146" s="13">
+      <c r="F147" s="13">
         <v>3</v>
       </c>
-      <c r="G146" s="13">
+      <c r="G147" s="13">
         <v>4</v>
       </c>
-      <c r="H146" s="13">
+      <c r="H147" s="13">
         <v>5</v>
       </c>
-      <c r="I146" s="13">
+      <c r="I147" s="13">
         <v>6</v>
       </c>
-      <c r="J146" s="13">
+      <c r="J147" s="13">
         <v>7</v>
       </c>
-      <c r="K146" s="13">
+      <c r="K147" s="13">
         <v>8</v>
       </c>
-      <c r="L146" s="13">
+      <c r="L147" s="13">
         <v>9</v>
       </c>
-      <c r="M146" s="13">
+      <c r="M147" s="13">
         <v>10</v>
       </c>
-      <c r="N146" s="13">
+      <c r="N147" s="13">
         <v>11</v>
       </c>
-      <c r="O146" s="13">
+      <c r="O147" s="13">
         <v>12</v>
       </c>
-      <c r="P146" s="13">
+      <c r="P147" s="13">
         <v>13</v>
       </c>
-      <c r="Q146" s="13">
+      <c r="Q147" s="13">
         <v>14</v>
       </c>
-      <c r="R146" s="13">
+      <c r="R147" s="13">
         <v>15</v>
       </c>
-      <c r="S146" s="13">
+      <c r="S147" s="13">
         <v>16</v>
       </c>
-      <c r="T146" s="13">
+      <c r="T147" s="13">
         <v>17</v>
       </c>
-      <c r="U146" s="13">
+      <c r="U147" s="13">
         <v>18</v>
       </c>
-      <c r="V146" s="13">
+      <c r="V147" s="13">
         <v>19</v>
       </c>
-      <c r="W146" s="13">
+      <c r="W147" s="13">
         <v>20</v>
       </c>
-      <c r="X146" s="13">
+      <c r="X147" s="13">
         <v>21</v>
       </c>
-      <c r="Y146" s="13">
+      <c r="Y147" s="13">
         <v>22</v>
       </c>
-      <c r="Z146" s="13">
+      <c r="Z147" s="13">
         <v>23</v>
       </c>
-      <c r="AA146" s="13">
+      <c r="AA147" s="13">
         <v>24</v>
       </c>
-      <c r="AB146" s="13">
+      <c r="AB147" s="13">
         <v>25</v>
       </c>
-      <c r="AC146" s="13">
+      <c r="AC147" s="13">
         <v>26</v>
       </c>
-      <c r="AD146" s="13">
+      <c r="AD147" s="13">
         <v>27</v>
       </c>
-      <c r="AE146" s="13">
+      <c r="AE147" s="13">
         <v>28</v>
       </c>
-      <c r="AF146" s="13">
+      <c r="AF147" s="13">
         <v>29</v>
       </c>
-      <c r="AG146" s="13">
+      <c r="AG147" s="13">
         <v>30</v>
       </c>
-      <c r="AH146" s="13">
+      <c r="AH147" s="13">
         <v>31</v>
       </c>
-      <c r="AI146" s="14" t="s">
+      <c r="AI147" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="AK146" s="35" t="s">
+      <c r="AK147" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AL146" s="36"/>
-      <c r="AM146" s="36"/>
-      <c r="AN146" s="36"/>
-      <c r="AO146" s="37"/>
-    </row>
-    <row r="147" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A147" s="6">
-        <v>1</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C147" s="6">
-        <v>3</v>
-      </c>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-      <c r="H147" s="7"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="7"/>
-      <c r="Q147" s="7"/>
-      <c r="R147" s="7"/>
-      <c r="S147" s="7"/>
-      <c r="T147" s="7"/>
-      <c r="U147" s="7"/>
-      <c r="V147" s="7"/>
-      <c r="W147" s="7"/>
-      <c r="X147" s="7"/>
-      <c r="Y147" s="7"/>
-      <c r="Z147" s="7"/>
-      <c r="AA147" s="7"/>
-      <c r="AB147" s="7"/>
-      <c r="AC147" s="7"/>
-      <c r="AD147" s="7"/>
-      <c r="AE147" s="7"/>
-      <c r="AF147" s="7"/>
-      <c r="AG147" s="7"/>
-      <c r="AH147" s="7"/>
-      <c r="AI147" s="6">
-        <f>C147-D147-E147-F147-G147-H147-I147-J147-K147-L147-M147-N147-O147-P147-Q147-R147-S147-T147-U147-V147-W147-X147-Y147-Z147-AA147-AB147-AC147-AD147-AE147-AF147-AG147-AH147</f>
-        <v>3</v>
-      </c>
-      <c r="AK147" s="2"/>
-      <c r="AL147" s="2"/>
-      <c r="AM147" s="2"/>
-      <c r="AN147" s="2"/>
-      <c r="AO147" s="2"/>
+      <c r="AL147" s="40"/>
+      <c r="AM147" s="40"/>
+      <c r="AN147" s="40"/>
+      <c r="AO147" s="41"/>
     </row>
     <row r="148" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C148" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
@@ -8052,8 +8092,8 @@
       <c r="AG148" s="7"/>
       <c r="AH148" s="7"/>
       <c r="AI148" s="6">
-        <f t="shared" ref="AI148:AI192" si="4">C148-D148-E148-F148-G148-H148-I148-J148-K148-L148-M148-N148-O148-P148-Q148-R148-S148-T148-U148-V148-W148-X148-Y148-Z148-AA148-AB148-AC148-AD148-AE148-AF148-AG148-AH148</f>
-        <v>1</v>
+        <f>C148-D148-E148-F148-G148-H148-I148-J148-K148-L148-M148-N148-O148-P148-Q148-R148-S148-T148-U148-V148-W148-X148-Y148-Z148-AA148-AB148-AC148-AD148-AE148-AF148-AG148-AH148</f>
+        <v>3</v>
       </c>
       <c r="AK148" s="2"/>
       <c r="AL148" s="2"/>
@@ -8063,12 +8103,12 @@
     </row>
     <row r="149" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C149" s="3">
+        <v>99</v>
+      </c>
+      <c r="C149" s="6">
         <v>1</v>
       </c>
       <c r="D149" s="7"/>
@@ -8103,7 +8143,7 @@
       <c r="AG149" s="7"/>
       <c r="AH149" s="7"/>
       <c r="AI149" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AI149:AI193" si="5">C149-D149-E149-F149-G149-H149-I149-J149-K149-L149-M149-N149-O149-P149-Q149-R149-S149-T149-U149-V149-W149-X149-Y149-Z149-AA149-AB149-AC149-AD149-AE149-AF149-AG149-AH149</f>
         <v>1</v>
       </c>
       <c r="AK149" s="2"/>
@@ -8114,10 +8154,10 @@
     </row>
     <row r="150" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C150" s="3">
         <v>1</v>
@@ -8154,7 +8194,7 @@
       <c r="AG150" s="7"/>
       <c r="AH150" s="7"/>
       <c r="AI150" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK150" s="2"/>
@@ -8165,13 +8205,13 @@
     </row>
     <row r="151" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C151" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
@@ -8205,8 +8245,8 @@
       <c r="AG151" s="7"/>
       <c r="AH151" s="7"/>
       <c r="AI151" s="6">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="AK151" s="2"/>
       <c r="AL151" s="2"/>
@@ -8216,13 +8256,13 @@
     </row>
     <row r="152" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C152" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
@@ -8256,8 +8296,8 @@
       <c r="AG152" s="7"/>
       <c r="AH152" s="7"/>
       <c r="AI152" s="6">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="AK152" s="2"/>
       <c r="AL152" s="2"/>
@@ -8267,10 +8307,10 @@
     </row>
     <row r="153" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C153" s="3">
         <v>5</v>
@@ -8307,7 +8347,7 @@
       <c r="AG153" s="7"/>
       <c r="AH153" s="7"/>
       <c r="AI153" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="AK153" s="2"/>
@@ -8318,13 +8358,13 @@
     </row>
     <row r="154" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C154" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
@@ -8358,8 +8398,8 @@
       <c r="AG154" s="7"/>
       <c r="AH154" s="7"/>
       <c r="AI154" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="AK154" s="2"/>
       <c r="AL154" s="2"/>
@@ -8369,13 +8409,13 @@
     </row>
     <row r="155" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C155" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
@@ -8409,8 +8449,8 @@
       <c r="AG155" s="7"/>
       <c r="AH155" s="7"/>
       <c r="AI155" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="AK155" s="2"/>
       <c r="AL155" s="2"/>
@@ -8420,10 +8460,10 @@
     </row>
     <row r="156" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C156" s="3">
         <v>1</v>
@@ -8460,7 +8500,7 @@
       <c r="AG156" s="7"/>
       <c r="AH156" s="7"/>
       <c r="AI156" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK156" s="2"/>
@@ -8471,10 +8511,10 @@
     </row>
     <row r="157" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C157" s="3">
         <v>1</v>
@@ -8511,7 +8551,7 @@
       <c r="AG157" s="7"/>
       <c r="AH157" s="7"/>
       <c r="AI157" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK157" s="2"/>
@@ -8522,10 +8562,10 @@
     </row>
     <row r="158" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C158" s="3">
         <v>1</v>
@@ -8562,7 +8602,7 @@
       <c r="AG158" s="7"/>
       <c r="AH158" s="7"/>
       <c r="AI158" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK158" s="2"/>
@@ -8573,10 +8613,10 @@
     </row>
     <row r="159" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C159" s="3">
         <v>1</v>
@@ -8613,7 +8653,7 @@
       <c r="AG159" s="7"/>
       <c r="AH159" s="7"/>
       <c r="AI159" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK159" s="2"/>
@@ -8624,10 +8664,10 @@
     </row>
     <row r="160" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C160" s="3">
         <v>1</v>
@@ -8664,7 +8704,7 @@
       <c r="AG160" s="7"/>
       <c r="AH160" s="7"/>
       <c r="AI160" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK160" s="2"/>
@@ -8675,10 +8715,10 @@
     </row>
     <row r="161" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C161" s="3">
         <v>1</v>
@@ -8715,7 +8755,7 @@
       <c r="AG161" s="7"/>
       <c r="AH161" s="7"/>
       <c r="AI161" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK161" s="2"/>
@@ -8726,10 +8766,10 @@
     </row>
     <row r="162" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C162" s="3">
         <v>1</v>
@@ -8766,7 +8806,7 @@
       <c r="AG162" s="7"/>
       <c r="AH162" s="7"/>
       <c r="AI162" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AK162" s="2"/>
@@ -8777,13 +8817,13 @@
     </row>
     <row r="163" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C163" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
@@ -8817,8 +8857,8 @@
       <c r="AG163" s="7"/>
       <c r="AH163" s="7"/>
       <c r="AI163" s="6">
-        <f t="shared" si="4"/>
-        <v>50</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="AK163" s="2"/>
       <c r="AL163" s="2"/>
@@ -8828,13 +8868,13 @@
     </row>
     <row r="164" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C164" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
@@ -8868,8 +8908,8 @@
       <c r="AG164" s="7"/>
       <c r="AH164" s="7"/>
       <c r="AI164" s="6">
-        <f t="shared" si="4"/>
-        <v>40</v>
+        <f t="shared" si="5"/>
+        <v>50</v>
       </c>
       <c r="AK164" s="2"/>
       <c r="AL164" s="2"/>
@@ -8879,13 +8919,13 @@
     </row>
     <row r="165" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C165" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
@@ -8919,8 +8959,8 @@
       <c r="AG165" s="7"/>
       <c r="AH165" s="7"/>
       <c r="AI165" s="6">
-        <f t="shared" si="4"/>
-        <v>41</v>
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
       <c r="AK165" s="2"/>
       <c r="AL165" s="2"/>
@@ -8930,13 +8970,13 @@
     </row>
     <row r="166" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C166" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
@@ -8970,8 +9010,8 @@
       <c r="AG166" s="7"/>
       <c r="AH166" s="7"/>
       <c r="AI166" s="6">
-        <f t="shared" si="4"/>
-        <v>42</v>
+        <f t="shared" si="5"/>
+        <v>41</v>
       </c>
       <c r="AK166" s="2"/>
       <c r="AL166" s="2"/>
@@ -8981,13 +9021,13 @@
     </row>
     <row r="167" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C167" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
@@ -9021,8 +9061,8 @@
       <c r="AG167" s="7"/>
       <c r="AH167" s="7"/>
       <c r="AI167" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>42</v>
       </c>
       <c r="AK167" s="2"/>
       <c r="AL167" s="2"/>
@@ -9032,13 +9072,13 @@
     </row>
     <row r="168" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C168" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -9072,8 +9112,8 @@
       <c r="AG168" s="7"/>
       <c r="AH168" s="7"/>
       <c r="AI168" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="AK168" s="2"/>
       <c r="AL168" s="2"/>
@@ -9083,10 +9123,10 @@
     </row>
     <row r="169" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C169" s="3">
         <v>2</v>
@@ -9123,7 +9163,7 @@
       <c r="AG169" s="7"/>
       <c r="AH169" s="7"/>
       <c r="AI169" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AK169" s="2"/>
@@ -9134,10 +9174,10 @@
     </row>
     <row r="170" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C170" s="3">
         <v>2</v>
@@ -9174,7 +9214,7 @@
       <c r="AG170" s="7"/>
       <c r="AH170" s="7"/>
       <c r="AI170" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="AK170" s="2"/>
@@ -9185,13 +9225,13 @@
     </row>
     <row r="171" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C171" s="6">
-        <v>31</v>
+        <v>121</v>
+      </c>
+      <c r="C171" s="3">
+        <v>2</v>
       </c>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
@@ -9225,8 +9265,8 @@
       <c r="AG171" s="7"/>
       <c r="AH171" s="7"/>
       <c r="AI171" s="6">
-        <f t="shared" si="4"/>
-        <v>31</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AK171" s="2"/>
       <c r="AL171" s="2"/>
@@ -9236,10 +9276,10 @@
     </row>
     <row r="172" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C172" s="6">
         <v>31</v>
@@ -9276,7 +9316,7 @@
       <c r="AG172" s="7"/>
       <c r="AH172" s="7"/>
       <c r="AI172" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="AK172" s="2"/>
@@ -9287,13 +9327,13 @@
     </row>
     <row r="173" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C173" s="6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
@@ -9327,8 +9367,8 @@
       <c r="AG173" s="7"/>
       <c r="AH173" s="7"/>
       <c r="AI173" s="6">
-        <f t="shared" si="4"/>
-        <v>29</v>
+        <f t="shared" si="5"/>
+        <v>31</v>
       </c>
       <c r="AK173" s="2"/>
       <c r="AL173" s="2"/>
@@ -9338,13 +9378,13 @@
     </row>
     <row r="174" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
+        <v>28</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C174" s="6">
         <v>29</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C174" s="6">
-        <v>30</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
@@ -9378,8 +9418,8 @@
       <c r="AG174" s="7"/>
       <c r="AH174" s="7"/>
       <c r="AI174" s="6">
-        <f t="shared" si="4"/>
-        <v>30</v>
+        <f t="shared" si="5"/>
+        <v>29</v>
       </c>
       <c r="AK174" s="2"/>
       <c r="AL174" s="2"/>
@@ -9389,13 +9429,13 @@
     </row>
     <row r="175" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
+        <v>29</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C175" s="6">
         <v>30</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C175" s="6">
-        <v>2</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
@@ -9429,8 +9469,8 @@
       <c r="AG175" s="7"/>
       <c r="AH175" s="7"/>
       <c r="AI175" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>30</v>
       </c>
       <c r="AK175" s="2"/>
       <c r="AL175" s="2"/>
@@ -9440,13 +9480,13 @@
     </row>
     <row r="176" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C176" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
@@ -9480,8 +9520,8 @@
       <c r="AG176" s="7"/>
       <c r="AH176" s="7"/>
       <c r="AI176" s="6">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AK176" s="2"/>
       <c r="AL176" s="2"/>
@@ -9491,10 +9531,10 @@
     </row>
     <row r="177" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C177" s="6">
         <v>4</v>
@@ -9531,7 +9571,7 @@
       <c r="AG177" s="7"/>
       <c r="AH177" s="7"/>
       <c r="AI177" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="AK177" s="2"/>
@@ -9542,10 +9582,10 @@
     </row>
     <row r="178" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C178" s="6">
         <v>4</v>
@@ -9582,7 +9622,7 @@
       <c r="AG178" s="7"/>
       <c r="AH178" s="7"/>
       <c r="AI178" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="AK178" s="2"/>
@@ -9593,13 +9633,13 @@
     </row>
     <row r="179" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C179" s="6">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
@@ -9633,8 +9673,8 @@
       <c r="AG179" s="7"/>
       <c r="AH179" s="7"/>
       <c r="AI179" s="6">
-        <f t="shared" si="4"/>
-        <v>17</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="AK179" s="2"/>
       <c r="AL179" s="2"/>
@@ -9644,13 +9684,13 @@
     </row>
     <row r="180" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C180" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
@@ -9684,8 +9724,8 @@
       <c r="AG180" s="7"/>
       <c r="AH180" s="7"/>
       <c r="AI180" s="6">
-        <f t="shared" si="4"/>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>17</v>
       </c>
       <c r="AK180" s="2"/>
       <c r="AL180" s="2"/>
@@ -9695,10 +9735,10 @@
     </row>
     <row r="181" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C181" s="6">
         <v>11</v>
@@ -9735,7 +9775,7 @@
       <c r="AG181" s="7"/>
       <c r="AH181" s="7"/>
       <c r="AI181" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AK181" s="2"/>
@@ -9746,10 +9786,10 @@
     </row>
     <row r="182" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C182" s="6">
         <v>11</v>
@@ -9786,7 +9826,7 @@
       <c r="AG182" s="7"/>
       <c r="AH182" s="7"/>
       <c r="AI182" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AK182" s="2"/>
@@ -9797,13 +9837,13 @@
     </row>
     <row r="183" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C183" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
@@ -9837,8 +9877,8 @@
       <c r="AG183" s="7"/>
       <c r="AH183" s="7"/>
       <c r="AI183" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="AK183" s="2"/>
       <c r="AL183" s="2"/>
@@ -9848,13 +9888,13 @@
     </row>
     <row r="184" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C184" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
@@ -9888,8 +9928,8 @@
       <c r="AG184" s="7"/>
       <c r="AH184" s="7"/>
       <c r="AI184" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AK184" s="2"/>
       <c r="AL184" s="2"/>
@@ -9899,10 +9939,10 @@
     </row>
     <row r="185" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C185" s="6">
         <v>3</v>
@@ -9939,7 +9979,7 @@
       <c r="AG185" s="7"/>
       <c r="AH185" s="7"/>
       <c r="AI185" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AK185" s="2"/>
@@ -9950,13 +9990,13 @@
     </row>
     <row r="186" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C186" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
@@ -9990,8 +10030,8 @@
       <c r="AG186" s="7"/>
       <c r="AH186" s="7"/>
       <c r="AI186" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="AK186" s="2"/>
       <c r="AL186" s="2"/>
@@ -10001,13 +10041,13 @@
     </row>
     <row r="187" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
-        <v>42</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>138</v>
+        <v>41</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="C187" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
@@ -10041,8 +10081,8 @@
       <c r="AG187" s="7"/>
       <c r="AH187" s="7"/>
       <c r="AI187" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AK187" s="2"/>
       <c r="AL187" s="2"/>
@@ -10052,10 +10092,10 @@
     </row>
     <row r="188" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C188" s="6">
         <v>3</v>
@@ -10092,7 +10132,7 @@
       <c r="AG188" s="7"/>
       <c r="AH188" s="7"/>
       <c r="AI188" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="AK188" s="2"/>
@@ -10103,13 +10143,13 @@
     </row>
     <row r="189" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C189" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
@@ -10143,8 +10183,8 @@
       <c r="AG189" s="7"/>
       <c r="AH189" s="7"/>
       <c r="AI189" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="AK189" s="2"/>
       <c r="AL189" s="2"/>
@@ -10154,13 +10194,13 @@
     </row>
     <row r="190" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C190" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
@@ -10194,8 +10234,8 @@
       <c r="AG190" s="7"/>
       <c r="AH190" s="7"/>
       <c r="AI190" s="6">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AK190" s="2"/>
       <c r="AL190" s="2"/>
@@ -10205,13 +10245,13 @@
     </row>
     <row r="191" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C191" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D191" s="7"/>
       <c r="E191" s="7"/>
@@ -10245,8 +10285,8 @@
       <c r="AG191" s="7"/>
       <c r="AH191" s="7"/>
       <c r="AI191" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="AK191" s="2"/>
       <c r="AL191" s="2"/>
@@ -10256,13 +10296,13 @@
     </row>
     <row r="192" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C192" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
@@ -10296,8 +10336,8 @@
       <c r="AG192" s="7"/>
       <c r="AH192" s="7"/>
       <c r="AI192" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>2</v>
       </c>
       <c r="AK192" s="2"/>
       <c r="AL192" s="2"/>
@@ -10305,169 +10345,180 @@
       <c r="AN192" s="2"/>
       <c r="AO192" s="2"/>
     </row>
-    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A198" s="38" t="s">
+    <row r="193" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A193" s="6">
+        <v>47</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C193" s="6">
+        <v>3</v>
+      </c>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
+      <c r="I193" s="7"/>
+      <c r="J193" s="7"/>
+      <c r="K193" s="7"/>
+      <c r="L193" s="7"/>
+      <c r="M193" s="7"/>
+      <c r="N193" s="7"/>
+      <c r="O193" s="7"/>
+      <c r="P193" s="7"/>
+      <c r="Q193" s="7"/>
+      <c r="R193" s="7"/>
+      <c r="S193" s="7"/>
+      <c r="T193" s="7"/>
+      <c r="U193" s="7"/>
+      <c r="V193" s="7"/>
+      <c r="W193" s="7"/>
+      <c r="X193" s="7"/>
+      <c r="Y193" s="7"/>
+      <c r="Z193" s="7"/>
+      <c r="AA193" s="7"/>
+      <c r="AB193" s="7"/>
+      <c r="AC193" s="7"/>
+      <c r="AD193" s="7"/>
+      <c r="AE193" s="7"/>
+      <c r="AF193" s="7"/>
+      <c r="AG193" s="7"/>
+      <c r="AH193" s="7"/>
+      <c r="AI193" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AK193" s="2"/>
+      <c r="AL193" s="2"/>
+      <c r="AM193" s="2"/>
+      <c r="AN193" s="2"/>
+      <c r="AO193" s="2"/>
+    </row>
+    <row r="199" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A199" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="B198" s="38"/>
-    </row>
-    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A199" s="12" t="s">
+      <c r="B199" s="35"/>
+    </row>
+    <row r="200" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A200" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B199" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C199" s="14" t="s">
+      <c r="B200" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D199" s="13">
-        <v>1</v>
-      </c>
-      <c r="E199" s="13">
+      <c r="D200" s="13">
+        <v>1</v>
+      </c>
+      <c r="E200" s="13">
         <v>2</v>
       </c>
-      <c r="F199" s="13">
+      <c r="F200" s="13">
         <v>3</v>
       </c>
-      <c r="G199" s="13">
+      <c r="G200" s="13">
         <v>4</v>
       </c>
-      <c r="H199" s="13">
+      <c r="H200" s="13">
         <v>5</v>
       </c>
-      <c r="I199" s="13">
+      <c r="I200" s="13">
         <v>6</v>
       </c>
-      <c r="J199" s="13">
+      <c r="J200" s="13">
         <v>7</v>
       </c>
-      <c r="K199" s="13">
+      <c r="K200" s="13">
         <v>8</v>
       </c>
-      <c r="L199" s="13">
+      <c r="L200" s="13">
         <v>9</v>
       </c>
-      <c r="M199" s="13">
+      <c r="M200" s="13">
         <v>10</v>
       </c>
-      <c r="N199" s="13">
+      <c r="N200" s="13">
         <v>11</v>
       </c>
-      <c r="O199" s="13">
+      <c r="O200" s="13">
         <v>12</v>
       </c>
-      <c r="P199" s="13">
+      <c r="P200" s="13">
         <v>13</v>
       </c>
-      <c r="Q199" s="13">
+      <c r="Q200" s="13">
         <v>14</v>
       </c>
-      <c r="R199" s="13">
+      <c r="R200" s="13">
         <v>15</v>
       </c>
-      <c r="S199" s="13">
+      <c r="S200" s="13">
         <v>16</v>
       </c>
-      <c r="T199" s="13">
+      <c r="T200" s="13">
         <v>17</v>
       </c>
-      <c r="U199" s="13">
+      <c r="U200" s="13">
         <v>18</v>
       </c>
-      <c r="V199" s="13">
+      <c r="V200" s="13">
         <v>19</v>
       </c>
-      <c r="W199" s="13">
+      <c r="W200" s="13">
         <v>20</v>
       </c>
-      <c r="X199" s="13">
+      <c r="X200" s="13">
         <v>21</v>
       </c>
-      <c r="Y199" s="13">
+      <c r="Y200" s="13">
         <v>22</v>
       </c>
-      <c r="Z199" s="13">
+      <c r="Z200" s="13">
         <v>23</v>
       </c>
-      <c r="AA199" s="13">
+      <c r="AA200" s="13">
         <v>24</v>
       </c>
-      <c r="AB199" s="13">
+      <c r="AB200" s="13">
         <v>25</v>
       </c>
-      <c r="AC199" s="13">
+      <c r="AC200" s="13">
         <v>26</v>
       </c>
-      <c r="AD199" s="13">
+      <c r="AD200" s="13">
         <v>27</v>
       </c>
-      <c r="AE199" s="13">
+      <c r="AE200" s="13">
         <v>28</v>
       </c>
-      <c r="AF199" s="13">
+      <c r="AF200" s="13">
         <v>29</v>
       </c>
-      <c r="AG199" s="13">
+      <c r="AG200" s="13">
         <v>30</v>
       </c>
-      <c r="AH199" s="13">
+      <c r="AH200" s="13">
         <v>31</v>
       </c>
-      <c r="AI199" s="14" t="s">
+      <c r="AI200" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A200" s="6">
-        <v>1</v>
-      </c>
-      <c r="B200" s="1" t="s">
+    <row r="201" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A201" s="6">
+        <v>1</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C200" s="6">
-        <v>1</v>
-      </c>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
-      <c r="H200" s="7"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
-      <c r="K200" s="7"/>
-      <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
-      <c r="N200" s="7"/>
-      <c r="O200" s="7"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="7"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="7"/>
-      <c r="T200" s="7"/>
-      <c r="U200" s="7"/>
-      <c r="V200" s="7"/>
-      <c r="W200" s="7"/>
-      <c r="X200" s="7"/>
-      <c r="Y200" s="7"/>
-      <c r="Z200" s="7"/>
-      <c r="AA200" s="7"/>
-      <c r="AB200" s="7"/>
-      <c r="AC200" s="7"/>
-      <c r="AD200" s="7"/>
-      <c r="AE200" s="7"/>
-      <c r="AF200" s="7"/>
-      <c r="AG200" s="7"/>
-      <c r="AH200" s="7"/>
-      <c r="AI200" s="6">
-        <f>C200-D200-E200-F200-G200-H200-I200-J200-K200-L200-M200-N200-O200-P200-Q200-R200-S200-T200-U200-V200-W200-X200-Y200-Z200-AA200-AB200-AC200-AD200-AE200-AF200-AG200-AH200</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A201" s="6"/>
-      <c r="B201" s="1"/>
-      <c r="C201" s="6"/>
+      <c r="C201" s="6">
+        <v>1</v>
+      </c>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -10500,11 +10551,11 @@
       <c r="AG201" s="7"/>
       <c r="AH201" s="7"/>
       <c r="AI201" s="6">
-        <f t="shared" ref="AI201:AI211" si="5">C201-D201-E201-F201-G201-H201-I201-J201-K201-L201-M201-N201-O201-P201-Q201-R201-S201-T201-U201-V201-W201-X201-Y201-Z201-AA201-AB201-AC201-AD201-AE201-AF201-AG201-AH201</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
+        <f>C201-D201-E201-F201-G201-H201-I201-J201-K201-L201-M201-N201-O201-P201-Q201-R201-S201-T201-U201-V201-W201-X201-Y201-Z201-AA201-AB201-AC201-AD201-AE201-AF201-AG201-AH201</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="1"/>
       <c r="C202" s="6"/>
@@ -10540,13 +10591,14 @@
       <c r="AG202" s="7"/>
       <c r="AH202" s="7"/>
       <c r="AI202" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AI202:AI212" si="6">C202-D202-E202-F202-G202-H202-I202-J202-K202-L202-M202-N202-O202-P202-Q202-R202-S202-T202-U202-V202-W202-X202-Y202-Z202-AA202-AB202-AC202-AD202-AE202-AF202-AG202-AH202</f>
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
-      <c r="B203" s="2"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="6"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -10579,14 +10631,13 @@
       <c r="AG203" s="7"/>
       <c r="AH203" s="7"/>
       <c r="AI203" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="2"/>
-      <c r="C204" s="6"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7"/>
       <c r="F204" s="7"/>
@@ -10619,11 +10670,11 @@
       <c r="AG204" s="7"/>
       <c r="AH204" s="7"/>
       <c r="AI204" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="2"/>
       <c r="C205" s="6"/>
@@ -10659,11 +10710,11 @@
       <c r="AG205" s="7"/>
       <c r="AH205" s="7"/>
       <c r="AI205" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="2"/>
       <c r="C206" s="6"/>
@@ -10699,11 +10750,11 @@
       <c r="AG206" s="7"/>
       <c r="AH206" s="7"/>
       <c r="AI206" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="2"/>
       <c r="C207" s="6"/>
@@ -10739,11 +10790,11 @@
       <c r="AG207" s="7"/>
       <c r="AH207" s="7"/>
       <c r="AI207" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="2"/>
       <c r="C208" s="6"/>
@@ -10779,7 +10830,7 @@
       <c r="AG208" s="7"/>
       <c r="AH208" s="7"/>
       <c r="AI208" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -10819,7 +10870,7 @@
       <c r="AG209" s="7"/>
       <c r="AH209" s="7"/>
       <c r="AI209" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -10859,7 +10910,7 @@
       <c r="AG210" s="7"/>
       <c r="AH210" s="7"/>
       <c r="AI210" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -10899,24 +10950,64 @@
       <c r="AG211" s="7"/>
       <c r="AH211" s="7"/>
       <c r="AI211" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A212" s="6"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="6"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
+      <c r="G212" s="7"/>
+      <c r="H212" s="7"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="7"/>
+      <c r="K212" s="7"/>
+      <c r="L212" s="7"/>
+      <c r="M212" s="7"/>
+      <c r="N212" s="7"/>
+      <c r="O212" s="7"/>
+      <c r="P212" s="7"/>
+      <c r="Q212" s="7"/>
+      <c r="R212" s="7"/>
+      <c r="S212" s="7"/>
+      <c r="T212" s="7"/>
+      <c r="U212" s="7"/>
+      <c r="V212" s="7"/>
+      <c r="W212" s="7"/>
+      <c r="X212" s="7"/>
+      <c r="Y212" s="7"/>
+      <c r="Z212" s="7"/>
+      <c r="AA212" s="7"/>
+      <c r="AB212" s="7"/>
+      <c r="AC212" s="7"/>
+      <c r="AD212" s="7"/>
+      <c r="AE212" s="7"/>
+      <c r="AF212" s="7"/>
+      <c r="AG212" s="7"/>
+      <c r="AH212" s="7"/>
+      <c r="AI212" s="6">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="AK147:AO147"/>
+    <mergeCell ref="AK3:AO3"/>
+    <mergeCell ref="AK34:AO34"/>
+    <mergeCell ref="AK53:AO53"/>
+    <mergeCell ref="AK105:AO105"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A146:B146"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A1:AI1"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="AK146:AO146"/>
-    <mergeCell ref="AK3:AO3"/>
-    <mergeCell ref="AK34:AO34"/>
-    <mergeCell ref="AK53:AO53"/>
-    <mergeCell ref="AK104:AO104"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
